--- a/dataset_agreed/saved_models/hyperparameter_optimized_runs/pointcloud_HPO_2048_run1/epoch_30/per_file_predictions_epoch_30.xlsx
+++ b/dataset_agreed/saved_models/hyperparameter_optimized_runs/pointcloud_HPO_2048_run1/epoch_30/per_file_predictions_epoch_30.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1024" uniqueCount="520">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1024" uniqueCount="524">
   <si>
     <t>Filename</t>
   </si>
@@ -808,772 +808,784 @@
     <t>0,1,1,0</t>
   </si>
   <si>
+    <t>0,0,0,0</t>
+  </si>
+  <si>
     <t>0,1,0,1</t>
   </si>
   <si>
-    <t>0.8901,0.0610,0.0323,0.0293</t>
-  </si>
-  <si>
-    <t>0.0387,0.0008,0.0044,0.9781</t>
-  </si>
-  <si>
-    <t>0.9118,0.0068,0.0083,0.0677</t>
-  </si>
-  <si>
-    <t>0.1874,0.0040,0.0233,0.8811</t>
-  </si>
-  <si>
-    <t>0.9988,0.0005,0.0000,0.0001</t>
-  </si>
-  <si>
-    <t>0.9980,0.0012,0.0001,0.0002</t>
-  </si>
-  <si>
-    <t>0.9988,0.0006,0.0001,0.0001</t>
-  </si>
-  <si>
-    <t>0.9991,0.0003,0.0000,0.0001</t>
-  </si>
-  <si>
-    <t>0.9923,0.0089,0.0006,0.0003</t>
-  </si>
-  <si>
-    <t>0.9981,0.0015,0.0001,0.0001</t>
-  </si>
-  <si>
-    <t>0.9985,0.0007,0.0001,0.0002</t>
-  </si>
-  <si>
-    <t>0.9981,0.0009,0.0001,0.0002</t>
-  </si>
-  <si>
-    <t>0.7209,0.0237,0.2915,0.0015</t>
-  </si>
-  <si>
-    <t>0.0982,0.0044,0.9176,0.0045</t>
-  </si>
-  <si>
-    <t>0.3205,0.0165,0.7932,0.0013</t>
-  </si>
-  <si>
-    <t>0.0148,0.0095,0.9781,0.0013</t>
-  </si>
-  <si>
-    <t>0.6557,0.0143,0.4590,0.0034</t>
-  </si>
-  <si>
-    <t>0.0176,0.9710,0.0072,0.0011</t>
-  </si>
-  <si>
-    <t>0.0222,0.9779,0.0031,0.0008</t>
-  </si>
-  <si>
-    <t>0.0774,0.9030,0.0202,0.0019</t>
-  </si>
-  <si>
-    <t>0.1500,0.8678,0.0097,0.0018</t>
-  </si>
-  <si>
-    <t>0.0101,0.9796,0.0088,0.0013</t>
-  </si>
-  <si>
-    <t>0.4712,0.0148,0.6485,0.0064</t>
-  </si>
-  <si>
-    <t>0.1593,0.0435,0.8812,0.0056</t>
-  </si>
-  <si>
-    <t>0.0058,0.0038,0.9929,0.0007</t>
-  </si>
-  <si>
-    <t>0.1329,0.0567,0.8056,0.0037</t>
-  </si>
-  <si>
-    <t>0.1117,0.0101,0.9401,0.0010</t>
-  </si>
-  <si>
-    <t>0.0557,0.0091,0.9657,0.0009</t>
-  </si>
-  <si>
-    <t>0.0093,0.0062,0.9837,0.0032</t>
-  </si>
-  <si>
-    <t>0.6560,0.3250,0.0363,0.0018</t>
-  </si>
-  <si>
-    <t>0.4091,0.1326,0.5302,0.0075</t>
-  </si>
-  <si>
-    <t>0.0560,0.0132,0.9593,0.0028</t>
-  </si>
-  <si>
-    <t>0.0177,0.8908,0.1058,0.0014</t>
-  </si>
-  <si>
-    <t>0.9002,0.0407,0.0506,0.0023</t>
-  </si>
-  <si>
-    <t>0.9005,0.0534,0.0351,0.0045</t>
-  </si>
-  <si>
-    <t>0.8768,0.1617,0.0089,0.0006</t>
-  </si>
-  <si>
-    <t>0.0458,0.9445,0.0184,0.0006</t>
-  </si>
-  <si>
-    <t>0.0342,0.6591,0.3993,0.0077</t>
-  </si>
-  <si>
-    <t>0.0334,0.0338,0.9792,0.0008</t>
-  </si>
-  <si>
-    <t>0.0161,0.1257,0.9711,0.0005</t>
-  </si>
-  <si>
-    <t>0.1259,0.0072,0.9151,0.0040</t>
-  </si>
-  <si>
-    <t>0.0086,0.0456,0.9846,0.0004</t>
-  </si>
-  <si>
-    <t>0.0022,0.9898,0.0495,0.0004</t>
-  </si>
-  <si>
-    <t>0.1197,0.0299,0.9058,0.0024</t>
-  </si>
-  <si>
-    <t>0.0484,0.7414,0.0338,0.7414</t>
-  </si>
-  <si>
-    <t>0.0012,0.9927,0.0062,0.0161</t>
-  </si>
-  <si>
-    <t>0.0015,0.9920,0.0125,0.0029</t>
-  </si>
-  <si>
-    <t>0.0004,0.9972,0.0272,0.0007</t>
-  </si>
-  <si>
-    <t>0.0102,0.0800,0.9790,0.0005</t>
-  </si>
-  <si>
-    <t>0.0028,0.0968,0.9924,0.0002</t>
-  </si>
-  <si>
-    <t>0.0353,0.0065,0.9793,0.0004</t>
-  </si>
-  <si>
-    <t>0.0048,0.0025,0.9942,0.0003</t>
-  </si>
-  <si>
-    <t>0.0169,0.0171,0.9804,0.0007</t>
-  </si>
-  <si>
-    <t>0.0077,0.0635,0.9732,0.0012</t>
-  </si>
-  <si>
-    <t>0.9851,0.0149,0.0022,0.0003</t>
-  </si>
-  <si>
-    <t>0.9896,0.0058,0.0027,0.0005</t>
-  </si>
-  <si>
-    <t>0.9783,0.0231,0.0015,0.0021</t>
-  </si>
-  <si>
-    <t>0.0931,0.1305,0.8419,0.0076</t>
-  </si>
-  <si>
-    <t>0.9973,0.0013,0.0003,0.0001</t>
+    <t>1,0,1,0</t>
+  </si>
+  <si>
+    <t>1,1,0,0</t>
+  </si>
+  <si>
+    <t>1,0,0,1</t>
+  </si>
+  <si>
+    <t>0.8156,0.0488,0.0779,0.0746</t>
+  </si>
+  <si>
+    <t>0.0854,0.0002,0.0006,0.9806</t>
+  </si>
+  <si>
+    <t>0.9242,0.0034,0.0047,0.0759</t>
+  </si>
+  <si>
+    <t>0.0505,0.0033,0.0038,0.9779</t>
+  </si>
+  <si>
+    <t>0.9990,0.0004,0.0001,0.0001</t>
+  </si>
+  <si>
+    <t>0.9966,0.0022,0.0003,0.0002</t>
+  </si>
+  <si>
+    <t>0.9980,0.0011,0.0002,0.0001</t>
+  </si>
+  <si>
+    <t>0.9978,0.0010,0.0002,0.0002</t>
+  </si>
+  <si>
+    <t>0.9974,0.0022,0.0001,0.0002</t>
+  </si>
+  <si>
+    <t>0.9979,0.0018,0.0001,0.0001</t>
+  </si>
+  <si>
+    <t>0.9979,0.0009,0.0002,0.0002</t>
+  </si>
+  <si>
+    <t>0.9980,0.0006,0.0001,0.0004</t>
+  </si>
+  <si>
+    <t>0.4644,0.0943,0.4213,0.0061</t>
+  </si>
+  <si>
+    <t>0.1248,0.0223,0.8955,0.0025</t>
+  </si>
+  <si>
+    <t>0.2667,0.0024,0.8879,0.0001</t>
+  </si>
+  <si>
+    <t>0.0190,0.0038,0.9828,0.0004</t>
+  </si>
+  <si>
+    <t>0.8033,0.0227,0.1889,0.0019</t>
+  </si>
+  <si>
+    <t>0.0077,0.9894,0.0024,0.0007</t>
+  </si>
+  <si>
+    <t>0.0088,0.9825,0.0057,0.0013</t>
+  </si>
+  <si>
+    <t>0.0238,0.9622,0.0063,0.0018</t>
+  </si>
+  <si>
+    <t>0.0203,0.9698,0.0043,0.0020</t>
+  </si>
+  <si>
+    <t>0.0055,0.9895,0.0022,0.0008</t>
+  </si>
+  <si>
+    <t>0.4941,0.0137,0.6326,0.0069</t>
+  </si>
+  <si>
+    <t>0.2492,0.0109,0.8348,0.0026</t>
+  </si>
+  <si>
+    <t>0.0133,0.0058,0.9879,0.0013</t>
+  </si>
+  <si>
+    <t>0.0047,0.0036,0.9894,0.0018</t>
+  </si>
+  <si>
+    <t>0.0443,0.0067,0.9742,0.0005</t>
+  </si>
+  <si>
+    <t>0.1757,0.0032,0.9031,0.0010</t>
+  </si>
+  <si>
+    <t>0.0143,0.0037,0.9854,0.0021</t>
+  </si>
+  <si>
+    <t>0.7606,0.1908,0.0480,0.0024</t>
+  </si>
+  <si>
+    <t>0.6852,0.2177,0.1102,0.0099</t>
+  </si>
+  <si>
+    <t>0.0440,0.0181,0.9644,0.0049</t>
+  </si>
+  <si>
+    <t>0.0231,0.6077,0.5171,0.0012</t>
+  </si>
+  <si>
+    <t>0.7938,0.0975,0.1035,0.0075</t>
+  </si>
+  <si>
+    <t>0.8279,0.0460,0.1071,0.0057</t>
+  </si>
+  <si>
+    <t>0.8772,0.1528,0.0116,0.0007</t>
+  </si>
+  <si>
+    <t>0.0518,0.9154,0.0814,0.0010</t>
+  </si>
+  <si>
+    <t>0.0178,0.9144,0.0939,0.0164</t>
+  </si>
+  <si>
+    <t>0.0169,0.0775,0.9872,0.0018</t>
+  </si>
+  <si>
+    <t>0.0938,0.0264,0.9272,0.0013</t>
+  </si>
+  <si>
+    <t>0.0208,0.0082,0.9874,0.0005</t>
+  </si>
+  <si>
+    <t>0.0100,0.1204,0.9781,0.0007</t>
+  </si>
+  <si>
+    <t>0.0035,0.9492,0.2155,0.0026</t>
+  </si>
+  <si>
+    <t>0.0325,0.0395,0.9545,0.0023</t>
+  </si>
+  <si>
+    <t>0.0305,0.8273,0.0268,0.7547</t>
+  </si>
+  <si>
+    <t>0.0012,0.9931,0.0098,0.0123</t>
+  </si>
+  <si>
+    <t>0.0007,0.9959,0.0046,0.0012</t>
+  </si>
+  <si>
+    <t>0.0005,0.9971,0.0101,0.0006</t>
+  </si>
+  <si>
+    <t>0.0048,0.0882,0.9880,0.0004</t>
+  </si>
+  <si>
+    <t>0.0024,0.0744,0.9946,0.0002</t>
+  </si>
+  <si>
+    <t>0.0283,0.0037,0.9825,0.0002</t>
+  </si>
+  <si>
+    <t>0.0165,0.0046,0.9881,0.0003</t>
+  </si>
+  <si>
+    <t>0.0067,0.0191,0.9924,0.0002</t>
+  </si>
+  <si>
+    <t>0.0128,0.0470,0.9700,0.0024</t>
+  </si>
+  <si>
+    <t>0.9903,0.0114,0.0010,0.0001</t>
+  </si>
+  <si>
+    <t>0.9935,0.0036,0.0015,0.0001</t>
+  </si>
+  <si>
+    <t>0.9910,0.0054,0.0009,0.0006</t>
+  </si>
+  <si>
+    <t>0.0997,0.0208,0.9247,0.0076</t>
+  </si>
+  <si>
+    <t>0.9947,0.0026,0.0008,0.0002</t>
+  </si>
+  <si>
+    <t>0.9970,0.0022,0.0002,0.0001</t>
+  </si>
+  <si>
+    <t>0.9919,0.0069,0.0010,0.0002</t>
+  </si>
+  <si>
+    <t>0.0009,0.9605,0.8687,0.0009</t>
+  </si>
+  <si>
+    <t>0.0054,0.0927,0.9861,0.0002</t>
+  </si>
+  <si>
+    <t>0.0121,0.1615,0.9544,0.0014</t>
+  </si>
+  <si>
+    <t>0.0003,0.9631,0.9572,0.0005</t>
+  </si>
+  <si>
+    <t>0.0058,0.0031,0.9938,0.0004</t>
+  </si>
+  <si>
+    <t>0.0097,0.9817,0.0093,0.0008</t>
+  </si>
+  <si>
+    <t>0.0139,0.9929,0.0006,0.0001</t>
+  </si>
+  <si>
+    <t>0.7194,0.0062,0.5690,0.0003</t>
+  </si>
+  <si>
+    <t>0.7085,0.0695,0.2880,0.0050</t>
+  </si>
+  <si>
+    <t>0.0126,0.0121,0.9916,0.0003</t>
+  </si>
+  <si>
+    <t>0.0011,0.9377,0.8366,0.0004</t>
+  </si>
+  <si>
+    <t>0.0008,0.7985,0.9486,0.0002</t>
+  </si>
+  <si>
+    <t>0.0022,0.9899,0.1484,0.0011</t>
+  </si>
+  <si>
+    <t>0.0012,0.9363,0.8500,0.0004</t>
+  </si>
+  <si>
+    <t>0.0183,0.0056,0.0583,0.9596</t>
+  </si>
+  <si>
+    <t>0.0274,0.0167,0.0028,0.9845</t>
+  </si>
+  <si>
+    <t>0.0017,0.0014,0.0017,0.9977</t>
+  </si>
+  <si>
+    <t>0.0427,0.0034,0.0122,0.9690</t>
+  </si>
+  <si>
+    <t>0.0202,0.0022,0.0110,0.9813</t>
+  </si>
+  <si>
+    <t>0.0205,0.0175,0.0199,0.9712</t>
+  </si>
+  <si>
+    <t>0.0002,0.9870,0.9248,0.0001</t>
+  </si>
+  <si>
+    <t>0.0015,0.8994,0.9498,0.0005</t>
+  </si>
+  <si>
+    <t>0.0071,0.8011,0.6575,0.0056</t>
+  </si>
+  <si>
+    <t>0.0039,0.9275,0.8328,0.0033</t>
+  </si>
+  <si>
+    <t>0.0020,0.9506,0.7020,0.0005</t>
+  </si>
+  <si>
+    <t>0.0014,0.9668,0.6654,0.0010</t>
+  </si>
+  <si>
+    <t>0.9984,0.0010,0.0001,0.0001</t>
+  </si>
+  <si>
+    <t>0.9968,0.0030,0.0002,0.0001</t>
+  </si>
+  <si>
+    <t>0.9951,0.0030,0.0006,0.0002</t>
+  </si>
+  <si>
+    <t>0.9951,0.0035,0.0005,0.0003</t>
+  </si>
+  <si>
+    <t>0.9970,0.0017,0.0003,0.0001</t>
+  </si>
+  <si>
+    <t>0.9985,0.0009,0.0000,0.0001</t>
+  </si>
+  <si>
+    <t>0.9961,0.0027,0.0004,0.0001</t>
+  </si>
+  <si>
+    <t>0.9918,0.0093,0.0011,0.0001</t>
+  </si>
+  <si>
+    <t>0.9982,0.0006,0.0003,0.0001</t>
   </si>
   <si>
     <t>0.9982,0.0009,0.0002,0.0001</t>
   </si>
   <si>
-    <t>0.9933,0.0060,0.0006,0.0003</t>
-  </si>
-  <si>
-    <t>0.0004,0.9880,0.7935,0.0009</t>
-  </si>
-  <si>
-    <t>0.0033,0.1109,0.9885,0.0002</t>
-  </si>
-  <si>
-    <t>0.0110,0.1774,0.9603,0.0021</t>
-  </si>
-  <si>
-    <t>0.0012,0.9644,0.8074,0.0011</t>
-  </si>
-  <si>
-    <t>0.0039,0.0013,0.9969,0.0002</t>
-  </si>
-  <si>
-    <t>0.0173,0.9707,0.0139,0.0007</t>
-  </si>
-  <si>
-    <t>0.0061,0.9944,0.0036,0.0001</t>
-  </si>
-  <si>
-    <t>0.9169,0.0090,0.1007,0.0003</t>
-  </si>
-  <si>
-    <t>0.7658,0.2282,0.0276,0.0009</t>
-  </si>
-  <si>
-    <t>0.0196,0.0148,0.9774,0.0006</t>
-  </si>
-  <si>
-    <t>0.0043,0.7134,0.9378,0.0010</t>
-  </si>
-  <si>
-    <t>0.0010,0.9707,0.5766,0.0004</t>
-  </si>
-  <si>
-    <t>0.0028,0.9844,0.2208,0.0008</t>
-  </si>
-  <si>
-    <t>0.0007,0.9333,0.9214,0.0006</t>
-  </si>
-  <si>
-    <t>0.0073,0.0011,0.1326,0.9492</t>
-  </si>
-  <si>
-    <t>0.0178,0.0061,0.0054,0.9860</t>
-  </si>
-  <si>
-    <t>0.0047,0.0015,0.0184,0.9880</t>
-  </si>
-  <si>
-    <t>0.0623,0.0063,0.0213,0.9522</t>
-  </si>
-  <si>
-    <t>0.0187,0.0017,0.0114,0.9843</t>
-  </si>
-  <si>
-    <t>0.0200,0.0170,0.0097,0.9782</t>
-  </si>
-  <si>
-    <t>0.0001,0.9933,0.9003,0.0001</t>
-  </si>
-  <si>
-    <t>0.0004,0.9100,0.9878,0.0001</t>
-  </si>
-  <si>
-    <t>0.0046,0.4590,0.9484,0.0006</t>
-  </si>
-  <si>
-    <t>0.0018,0.8714,0.9305,0.0011</t>
-  </si>
-  <si>
-    <t>0.0004,0.9730,0.8529,0.0001</t>
-  </si>
-  <si>
-    <t>0.0012,0.9091,0.9306,0.0007</t>
-  </si>
-  <si>
-    <t>0.9987,0.0009,0.0001,0.0001</t>
-  </si>
-  <si>
-    <t>0.9976,0.0014,0.0003,0.0000</t>
-  </si>
-  <si>
-    <t>0.9966,0.0026,0.0004,0.0001</t>
-  </si>
-  <si>
-    <t>0.9958,0.0029,0.0003,0.0002</t>
-  </si>
-  <si>
-    <t>0.9947,0.0055,0.0004,0.0002</t>
-  </si>
-  <si>
-    <t>0.9982,0.0012,0.0001,0.0001</t>
-  </si>
-  <si>
-    <t>0.9939,0.0048,0.0007,0.0003</t>
-  </si>
-  <si>
-    <t>0.9948,0.0040,0.0005,0.0002</t>
-  </si>
-  <si>
-    <t>0.9990,0.0004,0.0001,0.0001</t>
-  </si>
-  <si>
-    <t>0.9992,0.0006,0.0000,0.0000</t>
-  </si>
-  <si>
-    <t>0.9973,0.0010,0.0002,0.0005</t>
-  </si>
-  <si>
-    <t>0.9991,0.0003,0.0001,0.0001</t>
-  </si>
-  <si>
-    <t>0.9946,0.0023,0.0005,0.0009</t>
-  </si>
-  <si>
-    <t>0.9928,0.0120,0.0003,0.0002</t>
-  </si>
-  <si>
-    <t>0.9977,0.0010,0.0002,0.0002</t>
-  </si>
-  <si>
-    <t>0.9974,0.0010,0.0002,0.0003</t>
-  </si>
-  <si>
-    <t>0.0042,0.0025,0.9972,0.0002</t>
-  </si>
-  <si>
-    <t>0.0793,0.0447,0.9135,0.0026</t>
-  </si>
-  <si>
-    <t>0.8119,0.0100,0.2499,0.0073</t>
-  </si>
-  <si>
-    <t>0.0167,0.0015,0.9843,0.0011</t>
-  </si>
-  <si>
-    <t>0.0179,0.9727,0.0025,0.0022</t>
-  </si>
-  <si>
-    <t>0.0102,0.9849,0.0032,0.0008</t>
-  </si>
-  <si>
-    <t>0.3051,0.8492,0.0014,0.0004</t>
-  </si>
-  <si>
-    <t>0.5151,0.6199,0.0086,0.0005</t>
-  </si>
-  <si>
-    <t>0.0154,0.9825,0.0019,0.0006</t>
-  </si>
-  <si>
-    <t>0.0137,0.9851,0.0009,0.0003</t>
-  </si>
-  <si>
-    <t>0.6661,0.4608,0.0097,0.0008</t>
-  </si>
-  <si>
-    <t>0.3254,0.3487,0.2962,0.0224</t>
-  </si>
-  <si>
-    <t>0.0316,0.0047,0.9587,0.0115</t>
-  </si>
-  <si>
-    <t>0.1438,0.5973,0.2622,0.0356</t>
-  </si>
-  <si>
-    <t>0.1599,0.0057,0.9136,0.0009</t>
-  </si>
-  <si>
-    <t>0.4245,0.1863,0.5100,0.1369</t>
-  </si>
-  <si>
-    <t>0.0018,0.9945,0.0082,0.0006</t>
-  </si>
-  <si>
-    <t>0.0005,0.9976,0.0066,0.0011</t>
-  </si>
-  <si>
-    <t>0.0020,0.9898,0.0049,0.0151</t>
-  </si>
-  <si>
-    <t>0.0004,0.9979,0.0093,0.0006</t>
-  </si>
-  <si>
-    <t>0.0201,0.9706,0.0218,0.0003</t>
-  </si>
-  <si>
-    <t>0.8751,0.1628,0.0116,0.0009</t>
-  </si>
-  <si>
-    <t>0.9414,0.0597,0.0096,0.0004</t>
-  </si>
-  <si>
-    <t>0.9944,0.0020,0.0012,0.0005</t>
-  </si>
-  <si>
-    <t>0.9971,0.0010,0.0003,0.0002</t>
-  </si>
-  <si>
-    <t>0.9968,0.0019,0.0002,0.0002</t>
-  </si>
-  <si>
-    <t>0.9880,0.0021,0.0031,0.0017</t>
-  </si>
-  <si>
-    <t>0.9991,0.0004,0.0001,0.0000</t>
-  </si>
-  <si>
-    <t>0.9977,0.0006,0.0006,0.0001</t>
-  </si>
-  <si>
-    <t>0.9901,0.0035,0.0010,0.0019</t>
-  </si>
-  <si>
-    <t>0.9849,0.0058,0.0039,0.0006</t>
-  </si>
-  <si>
-    <t>0.0013,0.8231,0.9396,0.0003</t>
-  </si>
-  <si>
-    <t>0.0076,0.4357,0.8292,0.0004</t>
-  </si>
-  <si>
-    <t>0.0079,0.2136,0.9700,0.0004</t>
-  </si>
-  <si>
-    <t>0.0227,0.0451,0.9712,0.0006</t>
-  </si>
-  <si>
-    <t>0.9682,0.0044,0.0207,0.0008</t>
-  </si>
-  <si>
-    <t>0.8968,0.0070,0.1201,0.0023</t>
-  </si>
-  <si>
-    <t>0.1015,0.0014,0.9395,0.0014</t>
-  </si>
-  <si>
-    <t>0.7100,0.1155,0.1645,0.0062</t>
-  </si>
-  <si>
-    <t>0.0240,0.0036,0.0542,0.9622</t>
-  </si>
-  <si>
-    <t>0.0011,0.0005,0.0040,0.9973</t>
-  </si>
-  <si>
-    <t>0.0031,0.0297,0.0017,0.9950</t>
-  </si>
-  <si>
-    <t>0.0076,0.0003,0.0031,0.9943</t>
-  </si>
-  <si>
-    <t>0.0017,0.9498,0.6256,0.0032</t>
-  </si>
-  <si>
-    <t>0.9909,0.0049,0.0019,0.0003</t>
-  </si>
-  <si>
-    <t>0.0939,0.9113,0.0030,0.0228</t>
-  </si>
-  <si>
-    <t>0.9931,0.0019,0.0015,0.0004</t>
-  </si>
-  <si>
-    <t>0.8533,0.2419,0.0077,0.0012</t>
-  </si>
-  <si>
-    <t>0.9922,0.0011,0.0020,0.0010</t>
-  </si>
-  <si>
-    <t>0.7321,0.0092,0.0147,0.3926</t>
-  </si>
-  <si>
-    <t>0.9914,0.0021,0.0009,0.0019</t>
-  </si>
-  <si>
-    <t>0.0620,0.4996,0.3054,0.1374</t>
-  </si>
-  <si>
-    <t>0.7705,0.0009,0.0022,0.3912</t>
-  </si>
-  <si>
-    <t>0.7144,0.0023,0.0011,0.5311</t>
-  </si>
-  <si>
-    <t>0.3497,0.7014,0.0146,0.0026</t>
-  </si>
-  <si>
-    <t>0.9422,0.0165,0.0323,0.0017</t>
-  </si>
-  <si>
-    <t>0.8736,0.0458,0.0672,0.0016</t>
-  </si>
-  <si>
-    <t>0.2195,0.6374,0.0934,0.0322</t>
-  </si>
-  <si>
-    <t>0.9390,0.0536,0.0116,0.0008</t>
-  </si>
-  <si>
-    <t>0.8874,0.0436,0.0557,0.0011</t>
-  </si>
-  <si>
-    <t>0.9917,0.0036,0.0013,0.0009</t>
-  </si>
-  <si>
-    <t>0.9963,0.0028,0.0001,0.0005</t>
-  </si>
-  <si>
-    <t>0.9976,0.0004,0.0002,0.0004</t>
-  </si>
-  <si>
-    <t>0.9977,0.0005,0.0002,0.0003</t>
-  </si>
-  <si>
-    <t>0.9870,0.0057,0.0035,0.0007</t>
-  </si>
-  <si>
-    <t>0.9916,0.0028,0.0015,0.0009</t>
-  </si>
-  <si>
-    <t>0.9961,0.0022,0.0004,0.0003</t>
-  </si>
-  <si>
-    <t>0.9949,0.0011,0.0004,0.0014</t>
-  </si>
-  <si>
-    <t>0.8435,0.2316,0.0074,0.0006</t>
-  </si>
-  <si>
-    <t>0.4605,0.6404,0.0103,0.0013</t>
-  </si>
-  <si>
-    <t>0.8077,0.2784,0.0100,0.0017</t>
-  </si>
-  <si>
-    <t>0.0339,0.0055,0.9746,0.0024</t>
-  </si>
-  <si>
-    <t>0.9894,0.0126,0.0008,0.0003</t>
-  </si>
-  <si>
-    <t>0.9472,0.0395,0.0147,0.0016</t>
-  </si>
-  <si>
-    <t>0.9921,0.0037,0.0017,0.0002</t>
-  </si>
-  <si>
-    <t>0.9262,0.1103,0.0048,0.0016</t>
-  </si>
-  <si>
-    <t>0.0291,0.0101,0.9849,0.0004</t>
-  </si>
-  <si>
-    <t>0.9659,0.0258,0.0078,0.0006</t>
-  </si>
-  <si>
-    <t>0.0042,0.0155,0.9946,0.0002</t>
-  </si>
-  <si>
-    <t>0.0055,0.0634,0.9870,0.0006</t>
-  </si>
-  <si>
-    <t>0.0077,0.0179,0.9890,0.0006</t>
-  </si>
-  <si>
-    <t>0.0016,0.2019,0.9940,0.0004</t>
-  </si>
-  <si>
-    <t>0.0011,0.0513,0.9968,0.0003</t>
-  </si>
-  <si>
-    <t>0.0068,0.0040,0.9944,0.0005</t>
-  </si>
-  <si>
-    <t>0.0054,0.0033,0.9954,0.0003</t>
-  </si>
-  <si>
-    <t>0.2767,0.0528,0.7182,0.0213</t>
-  </si>
-  <si>
-    <t>0.2113,0.0083,0.8701,0.0009</t>
-  </si>
-  <si>
-    <t>0.6571,0.0257,0.3830,0.0101</t>
-  </si>
-  <si>
-    <t>0.1791,0.0293,0.8454,0.0021</t>
-  </si>
-  <si>
-    <t>0.1471,0.1253,0.6513,0.0009</t>
-  </si>
-  <si>
-    <t>0.3390,0.0497,0.7009,0.0037</t>
-  </si>
-  <si>
-    <t>0.4626,0.1866,0.3268,0.0061</t>
-  </si>
-  <si>
-    <t>0.6923,0.0090,0.4585,0.0015</t>
-  </si>
-  <si>
-    <t>0.6135,0.6119,0.0018,0.0019</t>
-  </si>
-  <si>
-    <t>0.9718,0.0667,0.0007,0.0004</t>
-  </si>
-  <si>
-    <t>0.9537,0.0467,0.0081,0.0011</t>
-  </si>
-  <si>
-    <t>0.9892,0.0139,0.0008,0.0002</t>
-  </si>
-  <si>
-    <t>0.9137,0.1330,0.0066,0.0004</t>
-  </si>
-  <si>
-    <t>0.4862,0.4142,0.0813,0.0213</t>
-  </si>
-  <si>
-    <t>0.9228,0.0063,0.0886,0.0005</t>
-  </si>
-  <si>
-    <t>0.7691,0.0109,0.2629,0.0101</t>
-  </si>
-  <si>
-    <t>0.2389,0.0041,0.8602,0.0020</t>
-  </si>
-  <si>
-    <t>0.6878,0.0043,0.3602,0.0110</t>
-  </si>
-  <si>
-    <t>0.0111,0.0191,0.9835,0.0023</t>
-  </si>
-  <si>
-    <t>0.0175,0.2389,0.9122,0.0151</t>
-  </si>
-  <si>
-    <t>0.0043,0.0628,0.9951,0.0002</t>
-  </si>
-  <si>
-    <t>0.0122,0.0148,0.9902,0.0002</t>
-  </si>
-  <si>
-    <t>0.0185,0.0499,0.9580,0.0012</t>
-  </si>
-  <si>
-    <t>0.9969,0.0012,0.0002,0.0004</t>
-  </si>
-  <si>
-    <t>0.9943,0.0021,0.0014,0.0002</t>
-  </si>
-  <si>
-    <t>0.9959,0.0030,0.0004,0.0002</t>
-  </si>
-  <si>
-    <t>0.9968,0.0025,0.0003,0.0000</t>
-  </si>
-  <si>
-    <t>0.9961,0.0022,0.0004,0.0002</t>
-  </si>
-  <si>
-    <t>0.9928,0.0058,0.0008,0.0002</t>
-  </si>
-  <si>
-    <t>0.9939,0.0045,0.0007,0.0003</t>
-  </si>
-  <si>
-    <t>0.9971,0.0012,0.0002,0.0003</t>
-  </si>
-  <si>
-    <t>0.0150,0.0204,0.9813,0.0018</t>
-  </si>
-  <si>
-    <t>0.3023,0.0779,0.6509,0.0031</t>
-  </si>
-  <si>
-    <t>0.7892,0.0182,0.1982,0.0114</t>
-  </si>
-  <si>
-    <t>0.0215,0.0031,0.9871,0.0006</t>
-  </si>
-  <si>
-    <t>0.0009,0.0051,0.9960,0.0011</t>
-  </si>
-  <si>
-    <t>0.0287,0.3321,0.7999,0.0045</t>
-  </si>
-  <si>
-    <t>0.0004,0.0044,0.9996,0.0000</t>
-  </si>
-  <si>
-    <t>0.0401,0.0158,0.9425,0.0019</t>
-  </si>
-  <si>
-    <t>0.0042,0.0082,0.9945,0.0006</t>
-  </si>
-  <si>
-    <t>0.0604,0.0156,0.9529,0.0006</t>
-  </si>
-  <si>
-    <t>0.2902,0.0948,0.6443,0.0086</t>
-  </si>
-  <si>
-    <t>0.5000,0.1164,0.3707,0.0076</t>
-  </si>
-  <si>
-    <t>0.5220,0.0051,0.6954,0.0017</t>
-  </si>
-  <si>
-    <t>0.8054,0.0131,0.2291,0.0069</t>
-  </si>
-  <si>
-    <t>0.9916,0.0095,0.0007,0.0003</t>
-  </si>
-  <si>
-    <t>0.9979,0.0017,0.0001,0.0001</t>
-  </si>
-  <si>
-    <t>0.9986,0.0008,0.0001,0.0001</t>
-  </si>
-  <si>
-    <t>0.9958,0.0025,0.0009,0.0001</t>
-  </si>
-  <si>
-    <t>0.9982,0.0007,0.0002,0.0001</t>
-  </si>
-  <si>
-    <t>0.9954,0.0033,0.0006,0.0002</t>
-  </si>
-  <si>
-    <t>0.9985,0.0007,0.0001,0.0001</t>
-  </si>
-  <si>
-    <t>0.9959,0.0025,0.0004,0.0002</t>
-  </si>
-  <si>
-    <t>0.0541,0.3538,0.7401,0.0077</t>
-  </si>
-  <si>
-    <t>0.0077,0.0548,0.9861,0.0002</t>
-  </si>
-  <si>
-    <t>0.0102,0.3286,0.8920,0.0013</t>
-  </si>
-  <si>
-    <t>0.0132,0.0369,0.9548,0.0017</t>
-  </si>
-  <si>
-    <t>0.0071,0.0077,0.9878,0.0006</t>
-  </si>
-  <si>
-    <t>0.0337,0.0620,0.9490,0.0135</t>
-  </si>
-  <si>
-    <t>0.0610,0.0492,0.9333,0.0013</t>
-  </si>
-  <si>
-    <t>0.0102,0.0996,0.9670,0.0142</t>
-  </si>
-  <si>
-    <t>0.9443,0.0009,0.0011,0.0857</t>
-  </si>
-  <si>
-    <t>0.1029,0.0056,0.0078,0.9574</t>
-  </si>
-  <si>
-    <t>0.3295,0.0036,0.0138,0.7618</t>
-  </si>
-  <si>
-    <t>0.0123,0.0005,0.0220,0.9822</t>
-  </si>
-  <si>
-    <t>0.1223,0.0006,0.0003,0.9760</t>
-  </si>
-  <si>
-    <t>0.8477,0.0278,0.0801,0.0602</t>
+    <t>0.9989,0.0003,0.0001,0.0001</t>
+  </si>
+  <si>
+    <t>0.9987,0.0005,0.0001,0.0001</t>
+  </si>
+  <si>
+    <t>0.9933,0.0037,0.0011,0.0004</t>
+  </si>
+  <si>
+    <t>0.9945,0.0085,0.0003,0.0001</t>
+  </si>
+  <si>
+    <t>0.9960,0.0015,0.0006,0.0003</t>
+  </si>
+  <si>
+    <t>0.9978,0.0008,0.0002,0.0001</t>
+  </si>
+  <si>
+    <t>0.0046,0.0035,0.9955,0.0003</t>
+  </si>
+  <si>
+    <t>0.0358,0.0911,0.9249,0.0031</t>
+  </si>
+  <si>
+    <t>0.5777,0.0202,0.4789,0.0181</t>
+  </si>
+  <si>
+    <t>0.0705,0.0070,0.9460,0.0044</t>
+  </si>
+  <si>
+    <t>0.0149,0.9789,0.0021,0.0011</t>
+  </si>
+  <si>
+    <t>0.0139,0.9774,0.0040,0.0010</t>
+  </si>
+  <si>
+    <t>0.6057,0.5423,0.0055,0.0005</t>
+  </si>
+  <si>
+    <t>0.3765,0.7722,0.0038,0.0009</t>
+  </si>
+  <si>
+    <t>0.0356,0.9624,0.0027,0.0016</t>
+  </si>
+  <si>
+    <t>0.0069,0.9897,0.0014,0.0004</t>
+  </si>
+  <si>
+    <t>0.7684,0.3058,0.0110,0.0014</t>
+  </si>
+  <si>
+    <t>0.5985,0.0783,0.3793,0.0205</t>
+  </si>
+  <si>
+    <t>0.0309,0.0274,0.9511,0.0059</t>
+  </si>
+  <si>
+    <t>0.4983,0.0926,0.4454,0.0455</t>
+  </si>
+  <si>
+    <t>0.5908,0.0054,0.6207,0.0003</t>
+  </si>
+  <si>
+    <t>0.4189,0.1071,0.5551,0.1015</t>
+  </si>
+  <si>
+    <t>0.0004,0.9983,0.0024,0.0003</t>
+  </si>
+  <si>
+    <t>0.0009,0.9949,0.0053,0.0048</t>
+  </si>
+  <si>
+    <t>0.0010,0.9934,0.0036,0.0269</t>
+  </si>
+  <si>
+    <t>0.0006,0.9970,0.0229,0.0007</t>
+  </si>
+  <si>
+    <t>0.0159,0.9693,0.0616,0.0002</t>
+  </si>
+  <si>
+    <t>0.9373,0.0687,0.0102,0.0004</t>
+  </si>
+  <si>
+    <t>0.8846,0.1483,0.0092,0.0005</t>
+  </si>
+  <si>
+    <t>0.9935,0.0031,0.0017,0.0002</t>
+  </si>
+  <si>
+    <t>0.9949,0.0036,0.0003,0.0003</t>
+  </si>
+  <si>
+    <t>0.9958,0.0015,0.0004,0.0005</t>
+  </si>
+  <si>
+    <t>0.9916,0.0022,0.0029,0.0003</t>
+  </si>
+  <si>
+    <t>0.9990,0.0003,0.0001,0.0001</t>
+  </si>
+  <si>
+    <t>0.9951,0.0020,0.0010,0.0002</t>
+  </si>
+  <si>
+    <t>0.9966,0.0019,0.0003,0.0002</t>
+  </si>
+  <si>
+    <t>0.9921,0.0020,0.0032,0.0002</t>
+  </si>
+  <si>
+    <t>0.0035,0.4619,0.9685,0.0003</t>
+  </si>
+  <si>
+    <t>0.0114,0.7838,0.6344,0.0012</t>
+  </si>
+  <si>
+    <t>0.0014,0.1140,0.9941,0.0001</t>
+  </si>
+  <si>
+    <t>0.0615,0.0874,0.9338,0.0012</t>
+  </si>
+  <si>
+    <t>0.9650,0.0089,0.0093,0.0037</t>
+  </si>
+  <si>
+    <t>0.5895,0.0444,0.4230,0.0195</t>
+  </si>
+  <si>
+    <t>0.5092,0.0022,0.7314,0.0009</t>
+  </si>
+  <si>
+    <t>0.5358,0.0164,0.5965,0.0017</t>
+  </si>
+  <si>
+    <t>0.0828,0.0104,0.0590,0.9047</t>
+  </si>
+  <si>
+    <t>0.0008,0.0005,0.0035,0.9979</t>
+  </si>
+  <si>
+    <t>0.0073,0.0162,0.0074,0.9879</t>
+  </si>
+  <si>
+    <t>0.0519,0.0051,0.0177,0.9552</t>
+  </si>
+  <si>
+    <t>0.0016,0.9690,0.4844,0.0017</t>
+  </si>
+  <si>
+    <t>0.9897,0.0050,0.0017,0.0005</t>
+  </si>
+  <si>
+    <t>0.3973,0.7213,0.0047,0.0047</t>
+  </si>
+  <si>
+    <t>0.9890,0.0038,0.0020,0.0010</t>
+  </si>
+  <si>
+    <t>0.5951,0.5708,0.0053,0.0020</t>
+  </si>
+  <si>
+    <t>0.9953,0.0007,0.0005,0.0012</t>
+  </si>
+  <si>
+    <t>0.5760,0.0071,0.0645,0.3657</t>
+  </si>
+  <si>
+    <t>0.9905,0.0025,0.0005,0.0030</t>
+  </si>
+  <si>
+    <t>0.1023,0.1447,0.6509,0.0475</t>
+  </si>
+  <si>
+    <t>0.3350,0.0017,0.0111,0.8177</t>
+  </si>
+  <si>
+    <t>0.9150,0.0033,0.0108,0.0714</t>
+  </si>
+  <si>
+    <t>0.6959,0.3259,0.0275,0.0037</t>
+  </si>
+  <si>
+    <t>0.9317,0.0319,0.0280,0.0026</t>
+  </si>
+  <si>
+    <t>0.9764,0.0094,0.0072,0.0006</t>
+  </si>
+  <si>
+    <t>0.3252,0.3043,0.4164,0.0125</t>
+  </si>
+  <si>
+    <t>0.8037,0.1136,0.0835,0.0036</t>
+  </si>
+  <si>
+    <t>0.7854,0.0921,0.1024,0.0027</t>
+  </si>
+  <si>
+    <t>0.9970,0.0008,0.0002,0.0007</t>
+  </si>
+  <si>
+    <t>0.9942,0.0019,0.0001,0.0022</t>
+  </si>
+  <si>
+    <t>0.9963,0.0017,0.0004,0.0003</t>
+  </si>
+  <si>
+    <t>0.9962,0.0009,0.0003,0.0008</t>
+  </si>
+  <si>
+    <t>0.9880,0.0074,0.0011,0.0011</t>
+  </si>
+  <si>
+    <t>0.9964,0.0024,0.0003,0.0002</t>
+  </si>
+  <si>
+    <t>0.9965,0.0012,0.0006,0.0003</t>
+  </si>
+  <si>
+    <t>0.9947,0.0017,0.0006,0.0007</t>
+  </si>
+  <si>
+    <t>0.9340,0.1006,0.0040,0.0003</t>
+  </si>
+  <si>
+    <t>0.8194,0.3001,0.0062,0.0004</t>
+  </si>
+  <si>
+    <t>0.9027,0.1461,0.0065,0.0011</t>
+  </si>
+  <si>
+    <t>0.0457,0.0182,0.9616,0.0031</t>
+  </si>
+  <si>
+    <t>0.9797,0.0335,0.0011,0.0004</t>
+  </si>
+  <si>
+    <t>0.9620,0.0166,0.0134,0.0013</t>
+  </si>
+  <si>
+    <t>0.9922,0.0034,0.0014,0.0004</t>
+  </si>
+  <si>
+    <t>0.9730,0.0445,0.0020,0.0005</t>
+  </si>
+  <si>
+    <t>0.0080,0.0177,0.9910,0.0006</t>
+  </si>
+  <si>
+    <t>0.9951,0.0037,0.0007,0.0001</t>
+  </si>
+  <si>
+    <t>0.0069,0.0218,0.9923,0.0002</t>
+  </si>
+  <si>
+    <t>0.0046,0.0827,0.9888,0.0012</t>
+  </si>
+  <si>
+    <t>0.0234,0.0160,0.9727,0.0012</t>
+  </si>
+  <si>
+    <t>0.0028,0.0489,0.9957,0.0003</t>
+  </si>
+  <si>
+    <t>0.0088,0.0512,0.9830,0.0007</t>
+  </si>
+  <si>
+    <t>0.0049,0.0046,0.9960,0.0002</t>
+  </si>
+  <si>
+    <t>0.0068,0.0040,0.9941,0.0002</t>
+  </si>
+  <si>
+    <t>0.1052,0.0219,0.9245,0.0013</t>
+  </si>
+  <si>
+    <t>0.1237,0.0142,0.8849,0.0047</t>
+  </si>
+  <si>
+    <t>0.2132,0.1159,0.6790,0.0102</t>
+  </si>
+  <si>
+    <t>0.2087,0.0722,0.7302,0.0053</t>
+  </si>
+  <si>
+    <t>0.2462,0.1865,0.3928,0.0013</t>
+  </si>
+  <si>
+    <t>0.2051,0.1152,0.7425,0.0145</t>
+  </si>
+  <si>
+    <t>0.5349,0.2296,0.2822,0.0096</t>
+  </si>
+  <si>
+    <t>0.3130,0.1884,0.5402,0.0128</t>
+  </si>
+  <si>
+    <t>0.9258,0.1776,0.0014,0.0003</t>
+  </si>
+  <si>
+    <t>0.8462,0.3155,0.0026,0.0004</t>
+  </si>
+  <si>
+    <t>0.9831,0.0361,0.0005,0.0003</t>
+  </si>
+  <si>
+    <t>0.9915,0.0069,0.0008,0.0003</t>
+  </si>
+  <si>
+    <t>0.9433,0.0680,0.0082,0.0011</t>
+  </si>
+  <si>
+    <t>0.7139,0.1408,0.1381,0.0145</t>
+  </si>
+  <si>
+    <t>0.8142,0.0028,0.3112,0.0012</t>
+  </si>
+  <si>
+    <t>0.6156,0.0974,0.3065,0.0139</t>
+  </si>
+  <si>
+    <t>0.8090,0.0053,0.3188,0.0010</t>
+  </si>
+  <si>
+    <t>0.1311,0.0226,0.8774,0.0064</t>
+  </si>
+  <si>
+    <t>0.0148,0.0139,0.9845,0.0018</t>
+  </si>
+  <si>
+    <t>0.0060,0.0614,0.9793,0.0015</t>
+  </si>
+  <si>
+    <t>0.0056,0.2559,0.9886,0.0005</t>
+  </si>
+  <si>
+    <t>0.0354,0.0319,0.9687,0.0006</t>
+  </si>
+  <si>
+    <t>0.0134,0.2992,0.8759,0.0014</t>
+  </si>
+  <si>
+    <t>0.9979,0.0007,0.0001,0.0003</t>
+  </si>
+  <si>
+    <t>0.9947,0.0028,0.0011,0.0002</t>
+  </si>
+  <si>
+    <t>0.9939,0.0067,0.0004,0.0003</t>
+  </si>
+  <si>
+    <t>0.9910,0.0096,0.0011,0.0001</t>
+  </si>
+  <si>
+    <t>0.9951,0.0023,0.0005,0.0003</t>
+  </si>
+  <si>
+    <t>0.9973,0.0034,0.0001,0.0001</t>
+  </si>
+  <si>
+    <t>0.9925,0.0064,0.0008,0.0004</t>
+  </si>
+  <si>
+    <t>0.9975,0.0012,0.0002,0.0001</t>
+  </si>
+  <si>
+    <t>0.0066,0.0063,0.9895,0.0026</t>
+  </si>
+  <si>
+    <t>0.1483,0.2670,0.5341,0.0037</t>
+  </si>
+  <si>
+    <t>0.7472,0.0655,0.1867,0.0153</t>
+  </si>
+  <si>
+    <t>0.0035,0.0073,0.9934,0.0005</t>
+  </si>
+  <si>
+    <t>0.0009,0.0041,0.9984,0.0004</t>
+  </si>
+  <si>
+    <t>0.0016,0.1858,0.9792,0.0005</t>
+  </si>
+  <si>
+    <t>0.0015,0.0055,0.9985,0.0001</t>
+  </si>
+  <si>
+    <t>0.0473,0.0082,0.9514,0.0020</t>
+  </si>
+  <si>
+    <t>0.0008,0.0028,0.9986,0.0005</t>
+  </si>
+  <si>
+    <t>0.0154,0.0062,0.9787,0.0010</t>
+  </si>
+  <si>
+    <t>0.0213,0.1383,0.9300,0.0027</t>
+  </si>
+  <si>
+    <t>0.8419,0.0070,0.2497,0.0013</t>
+  </si>
+  <si>
+    <t>0.1383,0.0035,0.9162,0.0021</t>
+  </si>
+  <si>
+    <t>0.9477,0.0032,0.0494,0.0030</t>
+  </si>
+  <si>
+    <t>0.9943,0.0037,0.0007,0.0003</t>
+  </si>
+  <si>
+    <t>0.9969,0.0017,0.0003,0.0002</t>
+  </si>
+  <si>
+    <t>0.9947,0.0029,0.0009,0.0003</t>
+  </si>
+  <si>
+    <t>0.9906,0.0091,0.0012,0.0002</t>
+  </si>
+  <si>
+    <t>0.9940,0.0033,0.0005,0.0007</t>
+  </si>
+  <si>
+    <t>0.9962,0.0015,0.0006,0.0002</t>
+  </si>
+  <si>
+    <t>0.9980,0.0015,0.0001,0.0001</t>
+  </si>
+  <si>
+    <t>0.9933,0.0052,0.0007,0.0004</t>
+  </si>
+  <si>
+    <t>0.0583,0.0350,0.8964,0.0017</t>
+  </si>
+  <si>
+    <t>0.0206,0.2948,0.8756,0.0024</t>
+  </si>
+  <si>
+    <t>0.0319,0.0328,0.9582,0.0004</t>
+  </si>
+  <si>
+    <t>0.0134,0.1118,0.9057,0.0036</t>
+  </si>
+  <si>
+    <t>0.0100,0.0079,0.9869,0.0010</t>
+  </si>
+  <si>
+    <t>0.0936,0.0331,0.8330,0.0690</t>
+  </si>
+  <si>
+    <t>0.0985,0.0092,0.9040,0.0188</t>
+  </si>
+  <si>
+    <t>0.0061,0.0889,0.9842,0.0049</t>
+  </si>
+  <si>
+    <t>0.9681,0.0088,0.0043,0.0109</t>
+  </si>
+  <si>
+    <t>0.0644,0.0105,0.0047,0.9719</t>
+  </si>
+  <si>
+    <t>0.5861,0.0029,0.0054,0.5882</t>
+  </si>
+  <si>
+    <t>0.0257,0.0003,0.0014,0.9901</t>
+  </si>
+  <si>
+    <t>0.0336,0.0005,0.0003,0.9935</t>
+  </si>
+  <si>
+    <t>0.8074,0.0350,0.0693,0.1059</t>
   </si>
 </sst>
 </file>
@@ -1959,7 +1971,7 @@
         <v>259</v>
       </c>
       <c r="D2" t="s">
-        <v>265</v>
+        <v>269</v>
       </c>
     </row>
     <row r="3" spans="1:4">
@@ -1973,7 +1985,7 @@
         <v>260</v>
       </c>
       <c r="D3" t="s">
-        <v>266</v>
+        <v>270</v>
       </c>
     </row>
     <row r="4" spans="1:4">
@@ -1987,7 +1999,7 @@
         <v>259</v>
       </c>
       <c r="D4" t="s">
-        <v>267</v>
+        <v>271</v>
       </c>
     </row>
     <row r="5" spans="1:4">
@@ -2001,7 +2013,7 @@
         <v>260</v>
       </c>
       <c r="D5" t="s">
-        <v>268</v>
+        <v>272</v>
       </c>
     </row>
     <row r="6" spans="1:4">
@@ -2015,7 +2027,7 @@
         <v>259</v>
       </c>
       <c r="D6" t="s">
-        <v>269</v>
+        <v>273</v>
       </c>
     </row>
     <row r="7" spans="1:4">
@@ -2029,7 +2041,7 @@
         <v>259</v>
       </c>
       <c r="D7" t="s">
-        <v>270</v>
+        <v>274</v>
       </c>
     </row>
     <row r="8" spans="1:4">
@@ -2043,7 +2055,7 @@
         <v>259</v>
       </c>
       <c r="D8" t="s">
-        <v>271</v>
+        <v>275</v>
       </c>
     </row>
     <row r="9" spans="1:4">
@@ -2057,7 +2069,7 @@
         <v>259</v>
       </c>
       <c r="D9" t="s">
-        <v>272</v>
+        <v>276</v>
       </c>
     </row>
     <row r="10" spans="1:4">
@@ -2071,7 +2083,7 @@
         <v>259</v>
       </c>
       <c r="D10" t="s">
-        <v>273</v>
+        <v>277</v>
       </c>
     </row>
     <row r="11" spans="1:4">
@@ -2085,7 +2097,7 @@
         <v>259</v>
       </c>
       <c r="D11" t="s">
-        <v>274</v>
+        <v>278</v>
       </c>
     </row>
     <row r="12" spans="1:4">
@@ -2099,7 +2111,7 @@
         <v>259</v>
       </c>
       <c r="D12" t="s">
-        <v>275</v>
+        <v>279</v>
       </c>
     </row>
     <row r="13" spans="1:4">
@@ -2113,7 +2125,7 @@
         <v>259</v>
       </c>
       <c r="D13" t="s">
-        <v>276</v>
+        <v>280</v>
       </c>
     </row>
     <row r="14" spans="1:4">
@@ -2124,10 +2136,10 @@
         <v>259</v>
       </c>
       <c r="C14" t="s">
-        <v>259</v>
+        <v>264</v>
       </c>
       <c r="D14" t="s">
-        <v>277</v>
+        <v>281</v>
       </c>
     </row>
     <row r="15" spans="1:4">
@@ -2141,7 +2153,7 @@
         <v>261</v>
       </c>
       <c r="D15" t="s">
-        <v>278</v>
+        <v>282</v>
       </c>
     </row>
     <row r="16" spans="1:4">
@@ -2155,7 +2167,7 @@
         <v>261</v>
       </c>
       <c r="D16" t="s">
-        <v>279</v>
+        <v>283</v>
       </c>
     </row>
     <row r="17" spans="1:4">
@@ -2169,7 +2181,7 @@
         <v>261</v>
       </c>
       <c r="D17" t="s">
-        <v>280</v>
+        <v>284</v>
       </c>
     </row>
     <row r="18" spans="1:4">
@@ -2183,7 +2195,7 @@
         <v>259</v>
       </c>
       <c r="D18" t="s">
-        <v>281</v>
+        <v>285</v>
       </c>
     </row>
     <row r="19" spans="1:4">
@@ -2197,7 +2209,7 @@
         <v>262</v>
       </c>
       <c r="D19" t="s">
-        <v>282</v>
+        <v>286</v>
       </c>
     </row>
     <row r="20" spans="1:4">
@@ -2211,7 +2223,7 @@
         <v>262</v>
       </c>
       <c r="D20" t="s">
-        <v>283</v>
+        <v>287</v>
       </c>
     </row>
     <row r="21" spans="1:4">
@@ -2225,7 +2237,7 @@
         <v>262</v>
       </c>
       <c r="D21" t="s">
-        <v>284</v>
+        <v>288</v>
       </c>
     </row>
     <row r="22" spans="1:4">
@@ -2239,7 +2251,7 @@
         <v>262</v>
       </c>
       <c r="D22" t="s">
-        <v>285</v>
+        <v>289</v>
       </c>
     </row>
     <row r="23" spans="1:4">
@@ -2253,7 +2265,7 @@
         <v>262</v>
       </c>
       <c r="D23" t="s">
-        <v>286</v>
+        <v>290</v>
       </c>
     </row>
     <row r="24" spans="1:4">
@@ -2267,7 +2279,7 @@
         <v>261</v>
       </c>
       <c r="D24" t="s">
-        <v>287</v>
+        <v>291</v>
       </c>
     </row>
     <row r="25" spans="1:4">
@@ -2281,7 +2293,7 @@
         <v>261</v>
       </c>
       <c r="D25" t="s">
-        <v>288</v>
+        <v>292</v>
       </c>
     </row>
     <row r="26" spans="1:4">
@@ -2295,7 +2307,7 @@
         <v>261</v>
       </c>
       <c r="D26" t="s">
-        <v>289</v>
+        <v>293</v>
       </c>
     </row>
     <row r="27" spans="1:4">
@@ -2309,7 +2321,7 @@
         <v>261</v>
       </c>
       <c r="D27" t="s">
-        <v>290</v>
+        <v>294</v>
       </c>
     </row>
     <row r="28" spans="1:4">
@@ -2323,7 +2335,7 @@
         <v>261</v>
       </c>
       <c r="D28" t="s">
-        <v>291</v>
+        <v>295</v>
       </c>
     </row>
     <row r="29" spans="1:4">
@@ -2337,7 +2349,7 @@
         <v>261</v>
       </c>
       <c r="D29" t="s">
-        <v>292</v>
+        <v>296</v>
       </c>
     </row>
     <row r="30" spans="1:4">
@@ -2351,7 +2363,7 @@
         <v>261</v>
       </c>
       <c r="D30" t="s">
-        <v>293</v>
+        <v>297</v>
       </c>
     </row>
     <row r="31" spans="1:4">
@@ -2365,7 +2377,7 @@
         <v>259</v>
       </c>
       <c r="D31" t="s">
-        <v>294</v>
+        <v>298</v>
       </c>
     </row>
     <row r="32" spans="1:4">
@@ -2376,10 +2388,10 @@
         <v>259</v>
       </c>
       <c r="C32" t="s">
-        <v>261</v>
+        <v>259</v>
       </c>
       <c r="D32" t="s">
-        <v>295</v>
+        <v>299</v>
       </c>
     </row>
     <row r="33" spans="1:4">
@@ -2393,7 +2405,7 @@
         <v>261</v>
       </c>
       <c r="D33" t="s">
-        <v>296</v>
+        <v>300</v>
       </c>
     </row>
     <row r="34" spans="1:4">
@@ -2404,10 +2416,10 @@
         <v>263</v>
       </c>
       <c r="C34" t="s">
-        <v>262</v>
+        <v>263</v>
       </c>
       <c r="D34" t="s">
-        <v>297</v>
+        <v>301</v>
       </c>
     </row>
     <row r="35" spans="1:4">
@@ -2421,7 +2433,7 @@
         <v>259</v>
       </c>
       <c r="D35" t="s">
-        <v>298</v>
+        <v>302</v>
       </c>
     </row>
     <row r="36" spans="1:4">
@@ -2435,7 +2447,7 @@
         <v>259</v>
       </c>
       <c r="D36" t="s">
-        <v>299</v>
+        <v>303</v>
       </c>
     </row>
     <row r="37" spans="1:4">
@@ -2449,7 +2461,7 @@
         <v>259</v>
       </c>
       <c r="D37" t="s">
-        <v>300</v>
+        <v>304</v>
       </c>
     </row>
     <row r="38" spans="1:4">
@@ -2463,7 +2475,7 @@
         <v>262</v>
       </c>
       <c r="D38" t="s">
-        <v>301</v>
+        <v>305</v>
       </c>
     </row>
     <row r="39" spans="1:4">
@@ -2477,7 +2489,7 @@
         <v>262</v>
       </c>
       <c r="D39" t="s">
-        <v>302</v>
+        <v>306</v>
       </c>
     </row>
     <row r="40" spans="1:4">
@@ -2491,7 +2503,7 @@
         <v>261</v>
       </c>
       <c r="D40" t="s">
-        <v>303</v>
+        <v>307</v>
       </c>
     </row>
     <row r="41" spans="1:4">
@@ -2505,7 +2517,7 @@
         <v>261</v>
       </c>
       <c r="D41" t="s">
-        <v>304</v>
+        <v>308</v>
       </c>
     </row>
     <row r="42" spans="1:4">
@@ -2519,7 +2531,7 @@
         <v>261</v>
       </c>
       <c r="D42" t="s">
-        <v>305</v>
+        <v>309</v>
       </c>
     </row>
     <row r="43" spans="1:4">
@@ -2533,7 +2545,7 @@
         <v>261</v>
       </c>
       <c r="D43" t="s">
-        <v>306</v>
+        <v>310</v>
       </c>
     </row>
     <row r="44" spans="1:4">
@@ -2547,7 +2559,7 @@
         <v>262</v>
       </c>
       <c r="D44" t="s">
-        <v>307</v>
+        <v>311</v>
       </c>
     </row>
     <row r="45" spans="1:4">
@@ -2561,7 +2573,7 @@
         <v>261</v>
       </c>
       <c r="D45" t="s">
-        <v>308</v>
+        <v>312</v>
       </c>
     </row>
     <row r="46" spans="1:4">
@@ -2572,10 +2584,10 @@
         <v>259</v>
       </c>
       <c r="C46" t="s">
-        <v>264</v>
+        <v>265</v>
       </c>
       <c r="D46" t="s">
-        <v>309</v>
+        <v>313</v>
       </c>
     </row>
     <row r="47" spans="1:4">
@@ -2589,7 +2601,7 @@
         <v>262</v>
       </c>
       <c r="D47" t="s">
-        <v>310</v>
+        <v>314</v>
       </c>
     </row>
     <row r="48" spans="1:4">
@@ -2603,7 +2615,7 @@
         <v>262</v>
       </c>
       <c r="D48" t="s">
-        <v>311</v>
+        <v>315</v>
       </c>
     </row>
     <row r="49" spans="1:4">
@@ -2617,7 +2629,7 @@
         <v>262</v>
       </c>
       <c r="D49" t="s">
-        <v>312</v>
+        <v>316</v>
       </c>
     </row>
     <row r="50" spans="1:4">
@@ -2631,7 +2643,7 @@
         <v>261</v>
       </c>
       <c r="D50" t="s">
-        <v>313</v>
+        <v>317</v>
       </c>
     </row>
     <row r="51" spans="1:4">
@@ -2645,7 +2657,7 @@
         <v>261</v>
       </c>
       <c r="D51" t="s">
-        <v>314</v>
+        <v>318</v>
       </c>
     </row>
     <row r="52" spans="1:4">
@@ -2659,7 +2671,7 @@
         <v>261</v>
       </c>
       <c r="D52" t="s">
-        <v>315</v>
+        <v>319</v>
       </c>
     </row>
     <row r="53" spans="1:4">
@@ -2673,7 +2685,7 @@
         <v>261</v>
       </c>
       <c r="D53" t="s">
-        <v>316</v>
+        <v>320</v>
       </c>
     </row>
     <row r="54" spans="1:4">
@@ -2687,7 +2699,7 @@
         <v>261</v>
       </c>
       <c r="D54" t="s">
-        <v>317</v>
+        <v>321</v>
       </c>
     </row>
     <row r="55" spans="1:4">
@@ -2701,7 +2713,7 @@
         <v>261</v>
       </c>
       <c r="D55" t="s">
-        <v>318</v>
+        <v>322</v>
       </c>
     </row>
     <row r="56" spans="1:4">
@@ -2715,7 +2727,7 @@
         <v>259</v>
       </c>
       <c r="D56" t="s">
-        <v>319</v>
+        <v>323</v>
       </c>
     </row>
     <row r="57" spans="1:4">
@@ -2729,7 +2741,7 @@
         <v>259</v>
       </c>
       <c r="D57" t="s">
-        <v>320</v>
+        <v>324</v>
       </c>
     </row>
     <row r="58" spans="1:4">
@@ -2743,7 +2755,7 @@
         <v>259</v>
       </c>
       <c r="D58" t="s">
-        <v>321</v>
+        <v>325</v>
       </c>
     </row>
     <row r="59" spans="1:4">
@@ -2757,7 +2769,7 @@
         <v>261</v>
       </c>
       <c r="D59" t="s">
-        <v>322</v>
+        <v>326</v>
       </c>
     </row>
     <row r="60" spans="1:4">
@@ -2771,7 +2783,7 @@
         <v>259</v>
       </c>
       <c r="D60" t="s">
-        <v>323</v>
+        <v>327</v>
       </c>
     </row>
     <row r="61" spans="1:4">
@@ -2785,7 +2797,7 @@
         <v>259</v>
       </c>
       <c r="D61" t="s">
-        <v>324</v>
+        <v>328</v>
       </c>
     </row>
     <row r="62" spans="1:4">
@@ -2799,7 +2811,7 @@
         <v>259</v>
       </c>
       <c r="D62" t="s">
-        <v>325</v>
+        <v>329</v>
       </c>
     </row>
     <row r="63" spans="1:4">
@@ -2813,7 +2825,7 @@
         <v>263</v>
       </c>
       <c r="D63" t="s">
-        <v>326</v>
+        <v>330</v>
       </c>
     </row>
     <row r="64" spans="1:4">
@@ -2827,7 +2839,7 @@
         <v>261</v>
       </c>
       <c r="D64" t="s">
-        <v>327</v>
+        <v>331</v>
       </c>
     </row>
     <row r="65" spans="1:4">
@@ -2841,7 +2853,7 @@
         <v>261</v>
       </c>
       <c r="D65" t="s">
-        <v>328</v>
+        <v>332</v>
       </c>
     </row>
     <row r="66" spans="1:4">
@@ -2855,7 +2867,7 @@
         <v>263</v>
       </c>
       <c r="D66" t="s">
-        <v>329</v>
+        <v>333</v>
       </c>
     </row>
     <row r="67" spans="1:4">
@@ -2869,7 +2881,7 @@
         <v>261</v>
       </c>
       <c r="D67" t="s">
-        <v>330</v>
+        <v>334</v>
       </c>
     </row>
     <row r="68" spans="1:4">
@@ -2883,7 +2895,7 @@
         <v>262</v>
       </c>
       <c r="D68" t="s">
-        <v>331</v>
+        <v>335</v>
       </c>
     </row>
     <row r="69" spans="1:4">
@@ -2897,7 +2909,7 @@
         <v>262</v>
       </c>
       <c r="D69" t="s">
-        <v>332</v>
+        <v>336</v>
       </c>
     </row>
     <row r="70" spans="1:4">
@@ -2908,10 +2920,10 @@
         <v>259</v>
       </c>
       <c r="C70" t="s">
-        <v>259</v>
+        <v>266</v>
       </c>
       <c r="D70" t="s">
-        <v>333</v>
+        <v>337</v>
       </c>
     </row>
     <row r="71" spans="1:4">
@@ -2925,7 +2937,7 @@
         <v>259</v>
       </c>
       <c r="D71" t="s">
-        <v>334</v>
+        <v>338</v>
       </c>
     </row>
     <row r="72" spans="1:4">
@@ -2939,7 +2951,7 @@
         <v>261</v>
       </c>
       <c r="D72" t="s">
-        <v>335</v>
+        <v>339</v>
       </c>
     </row>
     <row r="73" spans="1:4">
@@ -2953,7 +2965,7 @@
         <v>263</v>
       </c>
       <c r="D73" t="s">
-        <v>336</v>
+        <v>340</v>
       </c>
     </row>
     <row r="74" spans="1:4">
@@ -2967,7 +2979,7 @@
         <v>263</v>
       </c>
       <c r="D74" t="s">
-        <v>337</v>
+        <v>341</v>
       </c>
     </row>
     <row r="75" spans="1:4">
@@ -2981,7 +2993,7 @@
         <v>262</v>
       </c>
       <c r="D75" t="s">
-        <v>338</v>
+        <v>342</v>
       </c>
     </row>
     <row r="76" spans="1:4">
@@ -2995,7 +3007,7 @@
         <v>263</v>
       </c>
       <c r="D76" t="s">
-        <v>339</v>
+        <v>343</v>
       </c>
     </row>
     <row r="77" spans="1:4">
@@ -3009,7 +3021,7 @@
         <v>260</v>
       </c>
       <c r="D77" t="s">
-        <v>340</v>
+        <v>344</v>
       </c>
     </row>
     <row r="78" spans="1:4">
@@ -3023,7 +3035,7 @@
         <v>260</v>
       </c>
       <c r="D78" t="s">
-        <v>341</v>
+        <v>345</v>
       </c>
     </row>
     <row r="79" spans="1:4">
@@ -3037,7 +3049,7 @@
         <v>260</v>
       </c>
       <c r="D79" t="s">
-        <v>342</v>
+        <v>346</v>
       </c>
     </row>
     <row r="80" spans="1:4">
@@ -3051,7 +3063,7 @@
         <v>260</v>
       </c>
       <c r="D80" t="s">
-        <v>343</v>
+        <v>347</v>
       </c>
     </row>
     <row r="81" spans="1:4">
@@ -3065,7 +3077,7 @@
         <v>260</v>
       </c>
       <c r="D81" t="s">
-        <v>344</v>
+        <v>348</v>
       </c>
     </row>
     <row r="82" spans="1:4">
@@ -3079,7 +3091,7 @@
         <v>260</v>
       </c>
       <c r="D82" t="s">
-        <v>345</v>
+        <v>349</v>
       </c>
     </row>
     <row r="83" spans="1:4">
@@ -3093,7 +3105,7 @@
         <v>263</v>
       </c>
       <c r="D83" t="s">
-        <v>346</v>
+        <v>350</v>
       </c>
     </row>
     <row r="84" spans="1:4">
@@ -3107,7 +3119,7 @@
         <v>263</v>
       </c>
       <c r="D84" t="s">
-        <v>347</v>
+        <v>351</v>
       </c>
     </row>
     <row r="85" spans="1:4">
@@ -3118,10 +3130,10 @@
         <v>263</v>
       </c>
       <c r="C85" t="s">
-        <v>261</v>
+        <v>263</v>
       </c>
       <c r="D85" t="s">
-        <v>348</v>
+        <v>352</v>
       </c>
     </row>
     <row r="86" spans="1:4">
@@ -3135,7 +3147,7 @@
         <v>263</v>
       </c>
       <c r="D86" t="s">
-        <v>349</v>
+        <v>353</v>
       </c>
     </row>
     <row r="87" spans="1:4">
@@ -3149,7 +3161,7 @@
         <v>263</v>
       </c>
       <c r="D87" t="s">
-        <v>350</v>
+        <v>354</v>
       </c>
     </row>
     <row r="88" spans="1:4">
@@ -3163,7 +3175,7 @@
         <v>263</v>
       </c>
       <c r="D88" t="s">
-        <v>351</v>
+        <v>355</v>
       </c>
     </row>
     <row r="89" spans="1:4">
@@ -3177,7 +3189,7 @@
         <v>259</v>
       </c>
       <c r="D89" t="s">
-        <v>352</v>
+        <v>356</v>
       </c>
     </row>
     <row r="90" spans="1:4">
@@ -3191,7 +3203,7 @@
         <v>259</v>
       </c>
       <c r="D90" t="s">
-        <v>353</v>
+        <v>357</v>
       </c>
     </row>
     <row r="91" spans="1:4">
@@ -3205,7 +3217,7 @@
         <v>259</v>
       </c>
       <c r="D91" t="s">
-        <v>354</v>
+        <v>358</v>
       </c>
     </row>
     <row r="92" spans="1:4">
@@ -3219,7 +3231,7 @@
         <v>259</v>
       </c>
       <c r="D92" t="s">
-        <v>355</v>
+        <v>359</v>
       </c>
     </row>
     <row r="93" spans="1:4">
@@ -3233,7 +3245,7 @@
         <v>259</v>
       </c>
       <c r="D93" t="s">
-        <v>356</v>
+        <v>360</v>
       </c>
     </row>
     <row r="94" spans="1:4">
@@ -3247,7 +3259,7 @@
         <v>259</v>
       </c>
       <c r="D94" t="s">
-        <v>357</v>
+        <v>361</v>
       </c>
     </row>
     <row r="95" spans="1:4">
@@ -3261,7 +3273,7 @@
         <v>259</v>
       </c>
       <c r="D95" t="s">
-        <v>358</v>
+        <v>362</v>
       </c>
     </row>
     <row r="96" spans="1:4">
@@ -3275,7 +3287,7 @@
         <v>259</v>
       </c>
       <c r="D96" t="s">
-        <v>359</v>
+        <v>363</v>
       </c>
     </row>
     <row r="97" spans="1:4">
@@ -3289,7 +3301,7 @@
         <v>259</v>
       </c>
       <c r="D97" t="s">
-        <v>360</v>
+        <v>364</v>
       </c>
     </row>
     <row r="98" spans="1:4">
@@ -3303,7 +3315,7 @@
         <v>259</v>
       </c>
       <c r="D98" t="s">
-        <v>361</v>
+        <v>365</v>
       </c>
     </row>
     <row r="99" spans="1:4">
@@ -3317,7 +3329,7 @@
         <v>259</v>
       </c>
       <c r="D99" t="s">
-        <v>362</v>
+        <v>366</v>
       </c>
     </row>
     <row r="100" spans="1:4">
@@ -3331,7 +3343,7 @@
         <v>259</v>
       </c>
       <c r="D100" t="s">
-        <v>363</v>
+        <v>367</v>
       </c>
     </row>
     <row r="101" spans="1:4">
@@ -3345,7 +3357,7 @@
         <v>259</v>
       </c>
       <c r="D101" t="s">
-        <v>364</v>
+        <v>368</v>
       </c>
     </row>
     <row r="102" spans="1:4">
@@ -3359,7 +3371,7 @@
         <v>259</v>
       </c>
       <c r="D102" t="s">
-        <v>365</v>
+        <v>369</v>
       </c>
     </row>
     <row r="103" spans="1:4">
@@ -3373,7 +3385,7 @@
         <v>259</v>
       </c>
       <c r="D103" t="s">
-        <v>366</v>
+        <v>370</v>
       </c>
     </row>
     <row r="104" spans="1:4">
@@ -3387,7 +3399,7 @@
         <v>259</v>
       </c>
       <c r="D104" t="s">
-        <v>367</v>
+        <v>371</v>
       </c>
     </row>
     <row r="105" spans="1:4">
@@ -3401,7 +3413,7 @@
         <v>261</v>
       </c>
       <c r="D105" t="s">
-        <v>368</v>
+        <v>372</v>
       </c>
     </row>
     <row r="106" spans="1:4">
@@ -3415,7 +3427,7 @@
         <v>261</v>
       </c>
       <c r="D106" t="s">
-        <v>369</v>
+        <v>373</v>
       </c>
     </row>
     <row r="107" spans="1:4">
@@ -3429,7 +3441,7 @@
         <v>259</v>
       </c>
       <c r="D107" t="s">
-        <v>370</v>
+        <v>374</v>
       </c>
     </row>
     <row r="108" spans="1:4">
@@ -3443,7 +3455,7 @@
         <v>261</v>
       </c>
       <c r="D108" t="s">
-        <v>371</v>
+        <v>375</v>
       </c>
     </row>
     <row r="109" spans="1:4">
@@ -3457,7 +3469,7 @@
         <v>262</v>
       </c>
       <c r="D109" t="s">
-        <v>372</v>
+        <v>376</v>
       </c>
     </row>
     <row r="110" spans="1:4">
@@ -3471,7 +3483,7 @@
         <v>262</v>
       </c>
       <c r="D110" t="s">
-        <v>373</v>
+        <v>377</v>
       </c>
     </row>
     <row r="111" spans="1:4">
@@ -3482,10 +3494,10 @@
         <v>262</v>
       </c>
       <c r="C111" t="s">
-        <v>262</v>
+        <v>267</v>
       </c>
       <c r="D111" t="s">
-        <v>374</v>
+        <v>378</v>
       </c>
     </row>
     <row r="112" spans="1:4">
@@ -3499,7 +3511,7 @@
         <v>262</v>
       </c>
       <c r="D112" t="s">
-        <v>375</v>
+        <v>379</v>
       </c>
     </row>
     <row r="113" spans="1:4">
@@ -3513,7 +3525,7 @@
         <v>262</v>
       </c>
       <c r="D113" t="s">
-        <v>376</v>
+        <v>380</v>
       </c>
     </row>
     <row r="114" spans="1:4">
@@ -3527,7 +3539,7 @@
         <v>262</v>
       </c>
       <c r="D114" t="s">
-        <v>377</v>
+        <v>381</v>
       </c>
     </row>
     <row r="115" spans="1:4">
@@ -3541,7 +3553,7 @@
         <v>259</v>
       </c>
       <c r="D115" t="s">
-        <v>378</v>
+        <v>382</v>
       </c>
     </row>
     <row r="116" spans="1:4">
@@ -3555,7 +3567,7 @@
         <v>259</v>
       </c>
       <c r="D116" t="s">
-        <v>379</v>
+        <v>383</v>
       </c>
     </row>
     <row r="117" spans="1:4">
@@ -3569,7 +3581,7 @@
         <v>261</v>
       </c>
       <c r="D117" t="s">
-        <v>380</v>
+        <v>384</v>
       </c>
     </row>
     <row r="118" spans="1:4">
@@ -3580,10 +3592,10 @@
         <v>259</v>
       </c>
       <c r="C118" t="s">
-        <v>262</v>
+        <v>264</v>
       </c>
       <c r="D118" t="s">
-        <v>381</v>
+        <v>385</v>
       </c>
     </row>
     <row r="119" spans="1:4">
@@ -3594,10 +3606,10 @@
         <v>261</v>
       </c>
       <c r="C119" t="s">
-        <v>261</v>
+        <v>266</v>
       </c>
       <c r="D119" t="s">
-        <v>382</v>
+        <v>386</v>
       </c>
     </row>
     <row r="120" spans="1:4">
@@ -3611,7 +3623,7 @@
         <v>261</v>
       </c>
       <c r="D120" t="s">
-        <v>383</v>
+        <v>387</v>
       </c>
     </row>
     <row r="121" spans="1:4">
@@ -3625,7 +3637,7 @@
         <v>262</v>
       </c>
       <c r="D121" t="s">
-        <v>384</v>
+        <v>388</v>
       </c>
     </row>
     <row r="122" spans="1:4">
@@ -3639,7 +3651,7 @@
         <v>262</v>
       </c>
       <c r="D122" t="s">
-        <v>385</v>
+        <v>389</v>
       </c>
     </row>
     <row r="123" spans="1:4">
@@ -3653,7 +3665,7 @@
         <v>262</v>
       </c>
       <c r="D123" t="s">
-        <v>386</v>
+        <v>390</v>
       </c>
     </row>
     <row r="124" spans="1:4">
@@ -3667,7 +3679,7 @@
         <v>262</v>
       </c>
       <c r="D124" t="s">
-        <v>387</v>
+        <v>391</v>
       </c>
     </row>
     <row r="125" spans="1:4">
@@ -3681,7 +3693,7 @@
         <v>262</v>
       </c>
       <c r="D125" t="s">
-        <v>388</v>
+        <v>392</v>
       </c>
     </row>
     <row r="126" spans="1:4">
@@ -3695,7 +3707,7 @@
         <v>259</v>
       </c>
       <c r="D126" t="s">
-        <v>389</v>
+        <v>393</v>
       </c>
     </row>
     <row r="127" spans="1:4">
@@ -3709,7 +3721,7 @@
         <v>259</v>
       </c>
       <c r="D127" t="s">
-        <v>390</v>
+        <v>394</v>
       </c>
     </row>
     <row r="128" spans="1:4">
@@ -3723,7 +3735,7 @@
         <v>259</v>
       </c>
       <c r="D128" t="s">
-        <v>391</v>
+        <v>395</v>
       </c>
     </row>
     <row r="129" spans="1:4">
@@ -3737,7 +3749,7 @@
         <v>259</v>
       </c>
       <c r="D129" t="s">
-        <v>392</v>
+        <v>396</v>
       </c>
     </row>
     <row r="130" spans="1:4">
@@ -3751,7 +3763,7 @@
         <v>259</v>
       </c>
       <c r="D130" t="s">
-        <v>393</v>
+        <v>397</v>
       </c>
     </row>
     <row r="131" spans="1:4">
@@ -3765,7 +3777,7 @@
         <v>259</v>
       </c>
       <c r="D131" t="s">
-        <v>394</v>
+        <v>398</v>
       </c>
     </row>
     <row r="132" spans="1:4">
@@ -3779,7 +3791,7 @@
         <v>259</v>
       </c>
       <c r="D132" t="s">
-        <v>395</v>
+        <v>399</v>
       </c>
     </row>
     <row r="133" spans="1:4">
@@ -3793,7 +3805,7 @@
         <v>259</v>
       </c>
       <c r="D133" t="s">
-        <v>396</v>
+        <v>400</v>
       </c>
     </row>
     <row r="134" spans="1:4">
@@ -3807,7 +3819,7 @@
         <v>259</v>
       </c>
       <c r="D134" t="s">
-        <v>397</v>
+        <v>401</v>
       </c>
     </row>
     <row r="135" spans="1:4">
@@ -3821,7 +3833,7 @@
         <v>259</v>
       </c>
       <c r="D135" t="s">
-        <v>398</v>
+        <v>402</v>
       </c>
     </row>
     <row r="136" spans="1:4">
@@ -3832,10 +3844,10 @@
         <v>263</v>
       </c>
       <c r="C136" t="s">
-        <v>263</v>
+        <v>261</v>
       </c>
       <c r="D136" t="s">
-        <v>399</v>
+        <v>403</v>
       </c>
     </row>
     <row r="137" spans="1:4">
@@ -3846,10 +3858,10 @@
         <v>261</v>
       </c>
       <c r="C137" t="s">
-        <v>261</v>
+        <v>263</v>
       </c>
       <c r="D137" t="s">
-        <v>400</v>
+        <v>404</v>
       </c>
     </row>
     <row r="138" spans="1:4">
@@ -3863,7 +3875,7 @@
         <v>261</v>
       </c>
       <c r="D138" t="s">
-        <v>401</v>
+        <v>405</v>
       </c>
     </row>
     <row r="139" spans="1:4">
@@ -3877,7 +3889,7 @@
         <v>261</v>
       </c>
       <c r="D139" t="s">
-        <v>402</v>
+        <v>406</v>
       </c>
     </row>
     <row r="140" spans="1:4">
@@ -3891,7 +3903,7 @@
         <v>259</v>
       </c>
       <c r="D140" t="s">
-        <v>403</v>
+        <v>407</v>
       </c>
     </row>
     <row r="141" spans="1:4">
@@ -3905,7 +3917,7 @@
         <v>259</v>
       </c>
       <c r="D141" t="s">
-        <v>404</v>
+        <v>408</v>
       </c>
     </row>
     <row r="142" spans="1:4">
@@ -3916,10 +3928,10 @@
         <v>261</v>
       </c>
       <c r="C142" t="s">
-        <v>261</v>
+        <v>266</v>
       </c>
       <c r="D142" t="s">
-        <v>405</v>
+        <v>409</v>
       </c>
     </row>
     <row r="143" spans="1:4">
@@ -3930,10 +3942,10 @@
         <v>259</v>
       </c>
       <c r="C143" t="s">
-        <v>259</v>
+        <v>266</v>
       </c>
       <c r="D143" t="s">
-        <v>406</v>
+        <v>410</v>
       </c>
     </row>
     <row r="144" spans="1:4">
@@ -3947,7 +3959,7 @@
         <v>260</v>
       </c>
       <c r="D144" t="s">
-        <v>407</v>
+        <v>411</v>
       </c>
     </row>
     <row r="145" spans="1:4">
@@ -3961,7 +3973,7 @@
         <v>260</v>
       </c>
       <c r="D145" t="s">
-        <v>408</v>
+        <v>412</v>
       </c>
     </row>
     <row r="146" spans="1:4">
@@ -3975,7 +3987,7 @@
         <v>260</v>
       </c>
       <c r="D146" t="s">
-        <v>409</v>
+        <v>413</v>
       </c>
     </row>
     <row r="147" spans="1:4">
@@ -3989,7 +4001,7 @@
         <v>260</v>
       </c>
       <c r="D147" t="s">
-        <v>410</v>
+        <v>414</v>
       </c>
     </row>
     <row r="148" spans="1:4">
@@ -4000,10 +4012,10 @@
         <v>263</v>
       </c>
       <c r="C148" t="s">
-        <v>263</v>
+        <v>262</v>
       </c>
       <c r="D148" t="s">
-        <v>411</v>
+        <v>415</v>
       </c>
     </row>
     <row r="149" spans="1:4">
@@ -4017,7 +4029,7 @@
         <v>259</v>
       </c>
       <c r="D149" t="s">
-        <v>412</v>
+        <v>416</v>
       </c>
     </row>
     <row r="150" spans="1:4">
@@ -4031,7 +4043,7 @@
         <v>262</v>
       </c>
       <c r="D150" t="s">
-        <v>413</v>
+        <v>417</v>
       </c>
     </row>
     <row r="151" spans="1:4">
@@ -4045,7 +4057,7 @@
         <v>259</v>
       </c>
       <c r="D151" t="s">
-        <v>414</v>
+        <v>418</v>
       </c>
     </row>
     <row r="152" spans="1:4">
@@ -4056,10 +4068,10 @@
         <v>262</v>
       </c>
       <c r="C152" t="s">
-        <v>259</v>
+        <v>267</v>
       </c>
       <c r="D152" t="s">
-        <v>415</v>
+        <v>419</v>
       </c>
     </row>
     <row r="153" spans="1:4">
@@ -4073,7 +4085,7 @@
         <v>259</v>
       </c>
       <c r="D153" t="s">
-        <v>416</v>
+        <v>420</v>
       </c>
     </row>
     <row r="154" spans="1:4">
@@ -4087,7 +4099,7 @@
         <v>259</v>
       </c>
       <c r="D154" t="s">
-        <v>417</v>
+        <v>421</v>
       </c>
     </row>
     <row r="155" spans="1:4">
@@ -4101,7 +4113,7 @@
         <v>259</v>
       </c>
       <c r="D155" t="s">
-        <v>418</v>
+        <v>422</v>
       </c>
     </row>
     <row r="156" spans="1:4">
@@ -4112,10 +4124,10 @@
         <v>261</v>
       </c>
       <c r="C156" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D156" t="s">
-        <v>419</v>
+        <v>423</v>
       </c>
     </row>
     <row r="157" spans="1:4">
@@ -4126,10 +4138,10 @@
         <v>259</v>
       </c>
       <c r="C157" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="D157" t="s">
-        <v>420</v>
+        <v>424</v>
       </c>
     </row>
     <row r="158" spans="1:4">
@@ -4140,10 +4152,10 @@
         <v>259</v>
       </c>
       <c r="C158" t="s">
-        <v>260</v>
+        <v>259</v>
       </c>
       <c r="D158" t="s">
-        <v>421</v>
+        <v>425</v>
       </c>
     </row>
     <row r="159" spans="1:4">
@@ -4154,10 +4166,10 @@
         <v>259</v>
       </c>
       <c r="C159" t="s">
-        <v>262</v>
+        <v>259</v>
       </c>
       <c r="D159" t="s">
-        <v>422</v>
+        <v>426</v>
       </c>
     </row>
     <row r="160" spans="1:4">
@@ -4171,7 +4183,7 @@
         <v>259</v>
       </c>
       <c r="D160" t="s">
-        <v>423</v>
+        <v>427</v>
       </c>
     </row>
     <row r="161" spans="1:4">
@@ -4185,7 +4197,7 @@
         <v>259</v>
       </c>
       <c r="D161" t="s">
-        <v>424</v>
+        <v>428</v>
       </c>
     </row>
     <row r="162" spans="1:4">
@@ -4196,10 +4208,10 @@
         <v>262</v>
       </c>
       <c r="C162" t="s">
-        <v>262</v>
+        <v>264</v>
       </c>
       <c r="D162" t="s">
-        <v>425</v>
+        <v>429</v>
       </c>
     </row>
     <row r="163" spans="1:4">
@@ -4213,7 +4225,7 @@
         <v>259</v>
       </c>
       <c r="D163" t="s">
-        <v>426</v>
+        <v>430</v>
       </c>
     </row>
     <row r="164" spans="1:4">
@@ -4227,7 +4239,7 @@
         <v>259</v>
       </c>
       <c r="D164" t="s">
-        <v>427</v>
+        <v>431</v>
       </c>
     </row>
     <row r="165" spans="1:4">
@@ -4241,7 +4253,7 @@
         <v>259</v>
       </c>
       <c r="D165" t="s">
-        <v>428</v>
+        <v>432</v>
       </c>
     </row>
     <row r="166" spans="1:4">
@@ -4255,7 +4267,7 @@
         <v>259</v>
       </c>
       <c r="D166" t="s">
-        <v>429</v>
+        <v>433</v>
       </c>
     </row>
     <row r="167" spans="1:4">
@@ -4269,7 +4281,7 @@
         <v>259</v>
       </c>
       <c r="D167" t="s">
-        <v>430</v>
+        <v>434</v>
       </c>
     </row>
     <row r="168" spans="1:4">
@@ -4283,7 +4295,7 @@
         <v>259</v>
       </c>
       <c r="D168" t="s">
-        <v>431</v>
+        <v>435</v>
       </c>
     </row>
     <row r="169" spans="1:4">
@@ -4297,7 +4309,7 @@
         <v>259</v>
       </c>
       <c r="D169" t="s">
-        <v>432</v>
+        <v>436</v>
       </c>
     </row>
     <row r="170" spans="1:4">
@@ -4311,7 +4323,7 @@
         <v>259</v>
       </c>
       <c r="D170" t="s">
-        <v>433</v>
+        <v>437</v>
       </c>
     </row>
     <row r="171" spans="1:4">
@@ -4325,7 +4337,7 @@
         <v>259</v>
       </c>
       <c r="D171" t="s">
-        <v>434</v>
+        <v>438</v>
       </c>
     </row>
     <row r="172" spans="1:4">
@@ -4339,7 +4351,7 @@
         <v>259</v>
       </c>
       <c r="D172" t="s">
-        <v>435</v>
+        <v>439</v>
       </c>
     </row>
     <row r="173" spans="1:4">
@@ -4353,7 +4365,7 @@
         <v>259</v>
       </c>
       <c r="D173" t="s">
-        <v>436</v>
+        <v>440</v>
       </c>
     </row>
     <row r="174" spans="1:4">
@@ -4364,10 +4376,10 @@
         <v>259</v>
       </c>
       <c r="C174" t="s">
-        <v>262</v>
+        <v>259</v>
       </c>
       <c r="D174" t="s">
-        <v>437</v>
+        <v>441</v>
       </c>
     </row>
     <row r="175" spans="1:4">
@@ -4381,7 +4393,7 @@
         <v>259</v>
       </c>
       <c r="D175" t="s">
-        <v>438</v>
+        <v>442</v>
       </c>
     </row>
     <row r="176" spans="1:4">
@@ -4395,7 +4407,7 @@
         <v>261</v>
       </c>
       <c r="D176" t="s">
-        <v>439</v>
+        <v>443</v>
       </c>
     </row>
     <row r="177" spans="1:4">
@@ -4409,7 +4421,7 @@
         <v>259</v>
       </c>
       <c r="D177" t="s">
-        <v>440</v>
+        <v>444</v>
       </c>
     </row>
     <row r="178" spans="1:4">
@@ -4423,7 +4435,7 @@
         <v>259</v>
       </c>
       <c r="D178" t="s">
-        <v>441</v>
+        <v>445</v>
       </c>
     </row>
     <row r="179" spans="1:4">
@@ -4437,7 +4449,7 @@
         <v>259</v>
       </c>
       <c r="D179" t="s">
-        <v>442</v>
+        <v>446</v>
       </c>
     </row>
     <row r="180" spans="1:4">
@@ -4451,7 +4463,7 @@
         <v>259</v>
       </c>
       <c r="D180" t="s">
-        <v>443</v>
+        <v>447</v>
       </c>
     </row>
     <row r="181" spans="1:4">
@@ -4465,7 +4477,7 @@
         <v>261</v>
       </c>
       <c r="D181" t="s">
-        <v>444</v>
+        <v>448</v>
       </c>
     </row>
     <row r="182" spans="1:4">
@@ -4479,7 +4491,7 @@
         <v>259</v>
       </c>
       <c r="D182" t="s">
-        <v>445</v>
+        <v>449</v>
       </c>
     </row>
     <row r="183" spans="1:4">
@@ -4493,7 +4505,7 @@
         <v>261</v>
       </c>
       <c r="D183" t="s">
-        <v>446</v>
+        <v>450</v>
       </c>
     </row>
     <row r="184" spans="1:4">
@@ -4507,7 +4519,7 @@
         <v>261</v>
       </c>
       <c r="D184" t="s">
-        <v>447</v>
+        <v>451</v>
       </c>
     </row>
     <row r="185" spans="1:4">
@@ -4521,7 +4533,7 @@
         <v>261</v>
       </c>
       <c r="D185" t="s">
-        <v>448</v>
+        <v>452</v>
       </c>
     </row>
     <row r="186" spans="1:4">
@@ -4535,7 +4547,7 @@
         <v>261</v>
       </c>
       <c r="D186" t="s">
-        <v>449</v>
+        <v>453</v>
       </c>
     </row>
     <row r="187" spans="1:4">
@@ -4549,7 +4561,7 @@
         <v>261</v>
       </c>
       <c r="D187" t="s">
-        <v>450</v>
+        <v>454</v>
       </c>
     </row>
     <row r="188" spans="1:4">
@@ -4563,7 +4575,7 @@
         <v>261</v>
       </c>
       <c r="D188" t="s">
-        <v>451</v>
+        <v>455</v>
       </c>
     </row>
     <row r="189" spans="1:4">
@@ -4577,7 +4589,7 @@
         <v>261</v>
       </c>
       <c r="D189" t="s">
-        <v>452</v>
+        <v>456</v>
       </c>
     </row>
     <row r="190" spans="1:4">
@@ -4591,7 +4603,7 @@
         <v>261</v>
       </c>
       <c r="D190" t="s">
-        <v>453</v>
+        <v>457</v>
       </c>
     </row>
     <row r="191" spans="1:4">
@@ -4605,7 +4617,7 @@
         <v>261</v>
       </c>
       <c r="D191" t="s">
-        <v>454</v>
+        <v>458</v>
       </c>
     </row>
     <row r="192" spans="1:4">
@@ -4616,10 +4628,10 @@
         <v>259</v>
       </c>
       <c r="C192" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D192" t="s">
-        <v>455</v>
+        <v>459</v>
       </c>
     </row>
     <row r="193" spans="1:4">
@@ -4633,7 +4645,7 @@
         <v>261</v>
       </c>
       <c r="D193" t="s">
-        <v>456</v>
+        <v>460</v>
       </c>
     </row>
     <row r="194" spans="1:4">
@@ -4644,10 +4656,10 @@
         <v>261</v>
       </c>
       <c r="C194" t="s">
-        <v>261</v>
+        <v>264</v>
       </c>
       <c r="D194" t="s">
-        <v>457</v>
+        <v>461</v>
       </c>
     </row>
     <row r="195" spans="1:4">
@@ -4661,7 +4673,7 @@
         <v>261</v>
       </c>
       <c r="D195" t="s">
-        <v>458</v>
+        <v>462</v>
       </c>
     </row>
     <row r="196" spans="1:4">
@@ -4675,7 +4687,7 @@
         <v>259</v>
       </c>
       <c r="D196" t="s">
-        <v>459</v>
+        <v>463</v>
       </c>
     </row>
     <row r="197" spans="1:4">
@@ -4686,10 +4698,10 @@
         <v>259</v>
       </c>
       <c r="C197" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D197" t="s">
-        <v>460</v>
+        <v>464</v>
       </c>
     </row>
     <row r="198" spans="1:4">
@@ -4700,10 +4712,10 @@
         <v>259</v>
       </c>
       <c r="C198" t="s">
-        <v>262</v>
+        <v>259</v>
       </c>
       <c r="D198" t="s">
-        <v>461</v>
+        <v>465</v>
       </c>
     </row>
     <row r="199" spans="1:4">
@@ -4717,7 +4729,7 @@
         <v>259</v>
       </c>
       <c r="D199" t="s">
-        <v>462</v>
+        <v>466</v>
       </c>
     </row>
     <row r="200" spans="1:4">
@@ -4731,7 +4743,7 @@
         <v>259</v>
       </c>
       <c r="D200" t="s">
-        <v>463</v>
+        <v>467</v>
       </c>
     </row>
     <row r="201" spans="1:4">
@@ -4745,7 +4757,7 @@
         <v>259</v>
       </c>
       <c r="D201" t="s">
-        <v>464</v>
+        <v>468</v>
       </c>
     </row>
     <row r="202" spans="1:4">
@@ -4759,7 +4771,7 @@
         <v>259</v>
       </c>
       <c r="D202" t="s">
-        <v>465</v>
+        <v>469</v>
       </c>
     </row>
     <row r="203" spans="1:4">
@@ -4773,7 +4785,7 @@
         <v>259</v>
       </c>
       <c r="D203" t="s">
-        <v>466</v>
+        <v>470</v>
       </c>
     </row>
     <row r="204" spans="1:4">
@@ -4787,7 +4799,7 @@
         <v>259</v>
       </c>
       <c r="D204" t="s">
-        <v>467</v>
+        <v>471</v>
       </c>
     </row>
     <row r="205" spans="1:4">
@@ -4801,7 +4813,7 @@
         <v>259</v>
       </c>
       <c r="D205" t="s">
-        <v>468</v>
+        <v>472</v>
       </c>
     </row>
     <row r="206" spans="1:4">
@@ -4812,10 +4824,10 @@
         <v>261</v>
       </c>
       <c r="C206" t="s">
-        <v>261</v>
+        <v>259</v>
       </c>
       <c r="D206" t="s">
-        <v>469</v>
+        <v>473</v>
       </c>
     </row>
     <row r="207" spans="1:4">
@@ -4826,10 +4838,10 @@
         <v>259</v>
       </c>
       <c r="C207" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D207" t="s">
-        <v>470</v>
+        <v>474</v>
       </c>
     </row>
     <row r="208" spans="1:4">
@@ -4843,7 +4855,7 @@
         <v>261</v>
       </c>
       <c r="D208" t="s">
-        <v>471</v>
+        <v>475</v>
       </c>
     </row>
     <row r="209" spans="1:4">
@@ -4857,7 +4869,7 @@
         <v>261</v>
       </c>
       <c r="D209" t="s">
-        <v>472</v>
+        <v>476</v>
       </c>
     </row>
     <row r="210" spans="1:4">
@@ -4871,7 +4883,7 @@
         <v>261</v>
       </c>
       <c r="D210" t="s">
-        <v>473</v>
+        <v>477</v>
       </c>
     </row>
     <row r="211" spans="1:4">
@@ -4885,7 +4897,7 @@
         <v>261</v>
       </c>
       <c r="D211" t="s">
-        <v>474</v>
+        <v>478</v>
       </c>
     </row>
     <row r="212" spans="1:4">
@@ -4899,7 +4911,7 @@
         <v>261</v>
       </c>
       <c r="D212" t="s">
-        <v>475</v>
+        <v>479</v>
       </c>
     </row>
     <row r="213" spans="1:4">
@@ -4913,7 +4925,7 @@
         <v>259</v>
       </c>
       <c r="D213" t="s">
-        <v>476</v>
+        <v>480</v>
       </c>
     </row>
     <row r="214" spans="1:4">
@@ -4927,7 +4939,7 @@
         <v>259</v>
       </c>
       <c r="D214" t="s">
-        <v>477</v>
+        <v>481</v>
       </c>
     </row>
     <row r="215" spans="1:4">
@@ -4941,7 +4953,7 @@
         <v>259</v>
       </c>
       <c r="D215" t="s">
-        <v>478</v>
+        <v>482</v>
       </c>
     </row>
     <row r="216" spans="1:4">
@@ -4955,7 +4967,7 @@
         <v>259</v>
       </c>
       <c r="D216" t="s">
-        <v>479</v>
+        <v>483</v>
       </c>
     </row>
     <row r="217" spans="1:4">
@@ -4969,7 +4981,7 @@
         <v>259</v>
       </c>
       <c r="D217" t="s">
-        <v>480</v>
+        <v>484</v>
       </c>
     </row>
     <row r="218" spans="1:4">
@@ -4983,7 +4995,7 @@
         <v>259</v>
       </c>
       <c r="D218" t="s">
-        <v>481</v>
+        <v>485</v>
       </c>
     </row>
     <row r="219" spans="1:4">
@@ -4997,7 +5009,7 @@
         <v>259</v>
       </c>
       <c r="D219" t="s">
-        <v>482</v>
+        <v>486</v>
       </c>
     </row>
     <row r="220" spans="1:4">
@@ -5011,7 +5023,7 @@
         <v>259</v>
       </c>
       <c r="D220" t="s">
-        <v>483</v>
+        <v>487</v>
       </c>
     </row>
     <row r="221" spans="1:4">
@@ -5025,7 +5037,7 @@
         <v>261</v>
       </c>
       <c r="D221" t="s">
-        <v>484</v>
+        <v>488</v>
       </c>
     </row>
     <row r="222" spans="1:4">
@@ -5039,7 +5051,7 @@
         <v>261</v>
       </c>
       <c r="D222" t="s">
-        <v>485</v>
+        <v>489</v>
       </c>
     </row>
     <row r="223" spans="1:4">
@@ -5053,7 +5065,7 @@
         <v>259</v>
       </c>
       <c r="D223" t="s">
-        <v>486</v>
+        <v>490</v>
       </c>
     </row>
     <row r="224" spans="1:4">
@@ -5067,7 +5079,7 @@
         <v>261</v>
       </c>
       <c r="D224" t="s">
-        <v>487</v>
+        <v>491</v>
       </c>
     </row>
     <row r="225" spans="1:4">
@@ -5081,7 +5093,7 @@
         <v>261</v>
       </c>
       <c r="D225" t="s">
-        <v>488</v>
+        <v>492</v>
       </c>
     </row>
     <row r="226" spans="1:4">
@@ -5095,7 +5107,7 @@
         <v>261</v>
       </c>
       <c r="D226" t="s">
-        <v>489</v>
+        <v>493</v>
       </c>
     </row>
     <row r="227" spans="1:4">
@@ -5109,7 +5121,7 @@
         <v>261</v>
       </c>
       <c r="D227" t="s">
-        <v>490</v>
+        <v>494</v>
       </c>
     </row>
     <row r="228" spans="1:4">
@@ -5123,7 +5135,7 @@
         <v>261</v>
       </c>
       <c r="D228" t="s">
-        <v>491</v>
+        <v>495</v>
       </c>
     </row>
     <row r="229" spans="1:4">
@@ -5137,7 +5149,7 @@
         <v>261</v>
       </c>
       <c r="D229" t="s">
-        <v>492</v>
+        <v>496</v>
       </c>
     </row>
     <row r="230" spans="1:4">
@@ -5151,7 +5163,7 @@
         <v>261</v>
       </c>
       <c r="D230" t="s">
-        <v>493</v>
+        <v>497</v>
       </c>
     </row>
     <row r="231" spans="1:4">
@@ -5165,7 +5177,7 @@
         <v>261</v>
       </c>
       <c r="D231" t="s">
-        <v>494</v>
+        <v>498</v>
       </c>
     </row>
     <row r="232" spans="1:4">
@@ -5179,7 +5191,7 @@
         <v>259</v>
       </c>
       <c r="D232" t="s">
-        <v>495</v>
+        <v>499</v>
       </c>
     </row>
     <row r="233" spans="1:4">
@@ -5193,7 +5205,7 @@
         <v>261</v>
       </c>
       <c r="D233" t="s">
-        <v>496</v>
+        <v>500</v>
       </c>
     </row>
     <row r="234" spans="1:4">
@@ -5207,7 +5219,7 @@
         <v>259</v>
       </c>
       <c r="D234" t="s">
-        <v>497</v>
+        <v>501</v>
       </c>
     </row>
     <row r="235" spans="1:4">
@@ -5221,7 +5233,7 @@
         <v>259</v>
       </c>
       <c r="D235" t="s">
-        <v>498</v>
+        <v>502</v>
       </c>
     </row>
     <row r="236" spans="1:4">
@@ -5235,7 +5247,7 @@
         <v>259</v>
       </c>
       <c r="D236" t="s">
-        <v>499</v>
+        <v>503</v>
       </c>
     </row>
     <row r="237" spans="1:4">
@@ -5249,7 +5261,7 @@
         <v>259</v>
       </c>
       <c r="D237" t="s">
-        <v>500</v>
+        <v>504</v>
       </c>
     </row>
     <row r="238" spans="1:4">
@@ -5263,7 +5275,7 @@
         <v>259</v>
       </c>
       <c r="D238" t="s">
-        <v>501</v>
+        <v>505</v>
       </c>
     </row>
     <row r="239" spans="1:4">
@@ -5277,7 +5289,7 @@
         <v>259</v>
       </c>
       <c r="D239" t="s">
-        <v>502</v>
+        <v>506</v>
       </c>
     </row>
     <row r="240" spans="1:4">
@@ -5291,7 +5303,7 @@
         <v>259</v>
       </c>
       <c r="D240" t="s">
-        <v>503</v>
+        <v>507</v>
       </c>
     </row>
     <row r="241" spans="1:4">
@@ -5305,7 +5317,7 @@
         <v>259</v>
       </c>
       <c r="D241" t="s">
-        <v>504</v>
+        <v>508</v>
       </c>
     </row>
     <row r="242" spans="1:4">
@@ -5319,7 +5331,7 @@
         <v>259</v>
       </c>
       <c r="D242" t="s">
-        <v>505</v>
+        <v>509</v>
       </c>
     </row>
     <row r="243" spans="1:4">
@@ -5333,7 +5345,7 @@
         <v>261</v>
       </c>
       <c r="D243" t="s">
-        <v>506</v>
+        <v>510</v>
       </c>
     </row>
     <row r="244" spans="1:4">
@@ -5347,7 +5359,7 @@
         <v>261</v>
       </c>
       <c r="D244" t="s">
-        <v>507</v>
+        <v>511</v>
       </c>
     </row>
     <row r="245" spans="1:4">
@@ -5361,7 +5373,7 @@
         <v>261</v>
       </c>
       <c r="D245" t="s">
-        <v>508</v>
+        <v>512</v>
       </c>
     </row>
     <row r="246" spans="1:4">
@@ -5375,7 +5387,7 @@
         <v>261</v>
       </c>
       <c r="D246" t="s">
-        <v>509</v>
+        <v>513</v>
       </c>
     </row>
     <row r="247" spans="1:4">
@@ -5389,7 +5401,7 @@
         <v>261</v>
       </c>
       <c r="D247" t="s">
-        <v>510</v>
+        <v>514</v>
       </c>
     </row>
     <row r="248" spans="1:4">
@@ -5403,7 +5415,7 @@
         <v>261</v>
       </c>
       <c r="D248" t="s">
-        <v>511</v>
+        <v>515</v>
       </c>
     </row>
     <row r="249" spans="1:4">
@@ -5417,7 +5429,7 @@
         <v>261</v>
       </c>
       <c r="D249" t="s">
-        <v>512</v>
+        <v>516</v>
       </c>
     </row>
     <row r="250" spans="1:4">
@@ -5431,7 +5443,7 @@
         <v>261</v>
       </c>
       <c r="D250" t="s">
-        <v>513</v>
+        <v>517</v>
       </c>
     </row>
     <row r="251" spans="1:4">
@@ -5445,7 +5457,7 @@
         <v>259</v>
       </c>
       <c r="D251" t="s">
-        <v>514</v>
+        <v>518</v>
       </c>
     </row>
     <row r="252" spans="1:4">
@@ -5459,7 +5471,7 @@
         <v>260</v>
       </c>
       <c r="D252" t="s">
-        <v>515</v>
+        <v>519</v>
       </c>
     </row>
     <row r="253" spans="1:4">
@@ -5470,10 +5482,10 @@
         <v>260</v>
       </c>
       <c r="C253" t="s">
-        <v>260</v>
+        <v>268</v>
       </c>
       <c r="D253" t="s">
-        <v>516</v>
+        <v>520</v>
       </c>
     </row>
     <row r="254" spans="1:4">
@@ -5487,7 +5499,7 @@
         <v>260</v>
       </c>
       <c r="D254" t="s">
-        <v>517</v>
+        <v>521</v>
       </c>
     </row>
     <row r="255" spans="1:4">
@@ -5501,7 +5513,7 @@
         <v>260</v>
       </c>
       <c r="D255" t="s">
-        <v>518</v>
+        <v>522</v>
       </c>
     </row>
     <row r="256" spans="1:4">
@@ -5515,7 +5527,7 @@
         <v>259</v>
       </c>
       <c r="D256" t="s">
-        <v>519</v>
+        <v>523</v>
       </c>
     </row>
   </sheetData>
